--- a/FarmLife_仕様書.xlsx
+++ b/FarmLife_仕様書.xlsx
@@ -5,15 +5,20 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GA3\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GA3\Desktop\FarmLife\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12120" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="ゲームの動き" sheetId="1" r:id="rId1"/>
     <sheet name="操作" sheetId="2" r:id="rId2"/>
+    <sheet name="採取パート" sheetId="3" r:id="rId3"/>
+    <sheet name="購入パート" sheetId="4" r:id="rId4"/>
+    <sheet name="作物" sheetId="5" r:id="rId5"/>
+    <sheet name="パーク" sheetId="6" r:id="rId6"/>
+    <sheet name="ステージ" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -818,325 +823,6 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>493060</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>142315</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>438151</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>180415</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="テキスト ボックス 2"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2543736" y="1554256"/>
-          <a:ext cx="628650" cy="508747"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3600"/>
-            <a:t>W</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3600"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>485776</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>21291</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>428626</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>59391</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="テキスト ボックス 3"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2536452" y="2139203"/>
-          <a:ext cx="626409" cy="508747"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3600"/>
-            <a:t>S</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3600"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>534969</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>19386</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>480060</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>57486</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="テキスト ボックス 4"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3269204" y="2137298"/>
-          <a:ext cx="628650" cy="508747"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3600"/>
-            <a:t>D</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3600"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>428625</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>19386</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>371476</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>57486</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="テキスト ボックス 5"/>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1795743" y="2137298"/>
-          <a:ext cx="626409" cy="508747"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3600"/>
-            <a:t>A</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3600"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>190500</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>53376</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>201706</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>89647</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="正方形/長方形 1"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1557618" y="1465317"/>
-          <a:ext cx="4796117" cy="3566124"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>3</xdr:col>
@@ -1223,16 +909,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>392206</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>33618</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>168089</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>123264</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>89648</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>235324</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>22413</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1241,8 +927,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4493559" y="1882589"/>
-          <a:ext cx="1008530" cy="638735"/>
+          <a:off x="1490382" y="795619"/>
+          <a:ext cx="2162736" cy="638735"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1278,7 +964,7 @@
         <a:p>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3200"/>
-            <a:t>移動</a:t>
+            <a:t>操作方法</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1324,6 +1010,96 @@
           </a:ext>
         </a:extLst>
       </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>22411</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>190501</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>118241</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>151087</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="テキスト ボックス 12"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1388756" y="1609398"/>
+          <a:ext cx="6244382" cy="2088930"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2800"/>
+            <a:t>WASD</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2800"/>
+            <a:t>・・・移動</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2800"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2800"/>
+            <a:t>E</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2800"/>
+            <a:t>　　・・・ショップインタラクト</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2800"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2800"/>
+            <a:t>マウス左クリック・・・攻撃</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2800"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
@@ -1594,7 +1370,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FFFFFF00"/>
+    <tabColor rgb="FFFF0000"/>
   </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -1608,7 +1384,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor rgb="FF00B050"/>
+    <tabColor rgb="FFFFC000"/>
   </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
@@ -1617,4 +1393,54 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData/>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/FarmLife_仕様書.xlsx
+++ b/FarmLife_仕様書.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\takum\Desktop\FarmLife\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GA3\Desktop\FarmLife\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7829E50A-ABE1-4343-A529-C8EBAEE19E0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="ゲームの動き" sheetId="1" r:id="rId1"/>
@@ -32,7 +31,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -128,7 +127,9 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="lt1"/>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:solidFill>
@@ -168,16 +169,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>91586</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>586886</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>156063</xdr:rowOff>
+      <xdr:rowOff>161506</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>424961</xdr:colOff>
+      <xdr:colOff>234461</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>108438</xdr:rowOff>
+      <xdr:rowOff>113881</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -192,14 +193,14 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4912701" y="1848582"/>
-          <a:ext cx="1022106" cy="435952"/>
+          <a:off x="4701686" y="1837906"/>
+          <a:ext cx="1019175" cy="431346"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="lt1"/>
+          <a:srgbClr val="92D050"/>
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:solidFill>
@@ -239,16 +240,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>86456</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>576313</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>238856</xdr:rowOff>
+      <xdr:rowOff>233413</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>419831</xdr:colOff>
+      <xdr:colOff>223888</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>191231</xdr:rowOff>
+      <xdr:rowOff>185788</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -263,14 +264,17 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4907571" y="2656741"/>
-          <a:ext cx="1022106" cy="435952"/>
+          <a:off x="4691113" y="2628270"/>
+          <a:ext cx="1019175" cy="431347"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="lt1"/>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:solidFill>
@@ -311,15 +315,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>93052</xdr:colOff>
+      <xdr:colOff>93051</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>148737</xdr:rowOff>
+      <xdr:rowOff>165066</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>585422</xdr:colOff>
+      <xdr:colOff>585421</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>97448</xdr:rowOff>
+      <xdr:rowOff>113777</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -334,14 +338,17 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6265252" y="1815612"/>
-          <a:ext cx="1178170" cy="424961"/>
+          <a:off x="6265251" y="1841466"/>
+          <a:ext cx="1178170" cy="427682"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="lt1"/>
+          <a:schemeClr val="accent1">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:solidFill>
@@ -384,13 +391,13 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>470179</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>138113</xdr:rowOff>
+      <xdr:rowOff>138112</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
       <xdr:colOff>358077</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>143973</xdr:rowOff>
+      <xdr:rowOff>146288</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -402,13 +409,14 @@
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
+          <a:stCxn id="27" idx="3"/>
           <a:endCxn id="2" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="2527579" y="2043113"/>
-          <a:ext cx="573698" cy="5860"/>
+          <a:off x="2527579" y="2053998"/>
+          <a:ext cx="573698" cy="8176"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -445,13 +453,13 @@
       <xdr:col>6</xdr:col>
       <xdr:colOff>123825</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>132251</xdr:rowOff>
+      <xdr:rowOff>137693</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>91586</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>586886</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>138113</xdr:rowOff>
+      <xdr:rowOff>138112</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -469,8 +477,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="4238625" y="2037251"/>
-          <a:ext cx="653561" cy="5862"/>
+          <a:off x="4238625" y="2053579"/>
+          <a:ext cx="463061" cy="419"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -505,15 +513,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>445268</xdr:colOff>
+      <xdr:colOff>234461</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:rowOff>137693</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>85725</xdr:colOff>
+      <xdr:colOff>93051</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>126390</xdr:rowOff>
+      <xdr:rowOff>139421</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -524,74 +532,15 @@
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="5931668" y="2028825"/>
-          <a:ext cx="326257" cy="2565"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1">
-              <a:lumMod val="85000"/>
-              <a:lumOff val="15000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>597509</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>108438</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>602639</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>238856</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="21" name="直線矢印コネクタ 20">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000015000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
-          <a:stCxn id="3" idx="2"/>
-          <a:endCxn id="4" idx="0"/>
+          <a:stCxn id="3" idx="3"/>
+          <a:endCxn id="5" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="5418624" y="2284534"/>
-          <a:ext cx="5130" cy="372207"/>
+        <a:xfrm>
+          <a:off x="5720861" y="2053579"/>
+          <a:ext cx="544390" cy="1728"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -725,7 +674,9 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="lt1"/>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:solidFill>
@@ -836,61 +787,122 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>37000</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>400101</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>139212</xdr:rowOff>
+      <xdr:rowOff>113881</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>43962</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>484414</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>231530</xdr:rowOff>
+      <xdr:rowOff>233413</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="30" name="直線矢印コネクタ 29">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="5546846" y="2315308"/>
-          <a:ext cx="6962" cy="334107"/>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="19" name="グループ化 18"/>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="5185013" y="2231793"/>
+          <a:ext cx="84313" cy="354855"/>
+          <a:chOff x="5347658" y="2269252"/>
+          <a:chExt cx="182704" cy="359018"/>
         </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln>
-          <a:solidFill>
-            <a:schemeClr val="tx1">
-              <a:lumMod val="85000"/>
-              <a:lumOff val="15000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
+      </xdr:grpSpPr>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="21" name="直線矢印コネクタ 20">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000015000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr>
+            <a:stCxn id="3" idx="2"/>
+            <a:endCxn id="4" idx="0"/>
+          </xdr:cNvCxnSpPr>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipH="1">
+            <a:off x="5347658" y="2269252"/>
+            <a:ext cx="10573" cy="359018"/>
+          </a:xfrm>
+          <a:prstGeom prst="straightConnector1">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="85000"/>
+                <a:lumOff val="15000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:tailEnd type="triangle"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+      <xdr:cxnSp macro="">
+        <xdr:nvCxnSpPr>
+          <xdr:cNvPr id="30" name="直線矢印コネクタ 29">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-00001E000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvCxnSpPr/>
+        </xdr:nvCxnSpPr>
+        <xdr:spPr>
+          <a:xfrm flipV="1">
+            <a:off x="5523400" y="2294583"/>
+            <a:ext cx="6962" cy="331804"/>
+          </a:xfrm>
+          <a:prstGeom prst="straightConnector1">
+            <a:avLst/>
+          </a:prstGeom>
+          <a:ln>
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="85000"/>
+                <a:lumOff val="15000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:tailEnd type="triangle"/>
+          </a:ln>
+        </xdr:spPr>
+        <xdr:style>
+          <a:lnRef idx="1">
+            <a:schemeClr val="accent1"/>
+          </a:lnRef>
+          <a:fillRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:fillRef>
+          <a:effectRef idx="0">
+            <a:schemeClr val="accent1"/>
+          </a:effectRef>
+          <a:fontRef idx="minor">
+            <a:schemeClr val="tx1"/>
+          </a:fontRef>
+        </xdr:style>
+      </xdr:cxnSp>
+    </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
@@ -1119,15 +1131,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>340702</xdr:colOff>
+      <xdr:colOff>313488</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>148737</xdr:rowOff>
+      <xdr:rowOff>165065</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>147272</xdr:colOff>
+      <xdr:colOff>120058</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>97448</xdr:rowOff>
+      <xdr:rowOff>113776</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1142,14 +1154,17 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7884502" y="1815612"/>
-          <a:ext cx="1178170" cy="424961"/>
+          <a:off x="7857288" y="1841465"/>
+          <a:ext cx="1178170" cy="427682"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="lt1"/>
+          <a:schemeClr val="accent3">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:solidFill>
@@ -1190,15 +1205,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>588143</xdr:colOff>
+      <xdr:colOff>585421</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>123093</xdr:rowOff>
+      <xdr:rowOff>139420</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>340702</xdr:colOff>
+      <xdr:colOff>313488</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>135915</xdr:rowOff>
+      <xdr:rowOff>139421</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1210,13 +1225,14 @@
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
+          <a:stCxn id="5" idx="3"/>
           <a:endCxn id="13" idx="1"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="7446143" y="2028093"/>
-          <a:ext cx="438359" cy="12822"/>
+          <a:off x="7443421" y="2055306"/>
+          <a:ext cx="413867" cy="1"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1251,15 +1267,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>407168</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>40665</xdr:rowOff>
+      <xdr:colOff>234461</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>137693</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
+      <xdr:colOff>112102</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:rowOff>208818</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1270,12 +1286,15 @@
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="3" idx="3"/>
+          <a:endCxn id="24" idx="1"/>
+        </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5893568" y="2183790"/>
-          <a:ext cx="392932" cy="530835"/>
+          <a:off x="5720861" y="2053579"/>
+          <a:ext cx="563441" cy="789582"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -1340,7 +1359,10 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="lt1"/>
+          <a:schemeClr val="accent2">
+            <a:lumMod val="60000"/>
+            <a:lumOff val="40000"/>
+          </a:schemeClr>
         </a:solidFill>
         <a:ln w="9525" cmpd="sng">
           <a:solidFill>
@@ -1543,6 +1565,68 @@
         </a:p>
       </xdr:txBody>
     </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>604472</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>139420</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>313488</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>208818</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="39" name="直線矢印コネクタ 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB8B47D1-C87F-4E60-83DE-041FD5896B98}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="24" idx="3"/>
+          <a:endCxn id="13" idx="1"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="7462472" y="2055306"/>
+          <a:ext cx="394816" cy="787855"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1">
+              <a:lumMod val="85000"/>
+              <a:lumOff val="15000"/>
+            </a:schemeClr>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -1623,15 +1707,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>13</xdr:col>
-      <xdr:colOff>24334</xdr:colOff>
+      <xdr:colOff>53198</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>190659</xdr:rowOff>
+      <xdr:rowOff>233954</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
-      <xdr:colOff>519634</xdr:colOff>
+      <xdr:colOff>548498</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>76201</xdr:rowOff>
+      <xdr:rowOff>119496</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1646,8 +1730,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8939734" y="1619409"/>
-          <a:ext cx="8039100" cy="3219292"/>
+          <a:off x="9058653" y="1705999"/>
+          <a:ext cx="8115300" cy="3320315"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2161,6 +2245,66 @@
         </a:p>
         <a:p>
           <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>595313</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>14883</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>565547</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>104180</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="9" name="正方形/長方形 8"/>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4702969" y="2872383"/>
+          <a:ext cx="4762500" cy="4375547"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent6">
+            <a:lumMod val="40000"/>
+            <a:lumOff val="60000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -3285,16 +3429,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>584994</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>96242</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>451048</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>140891</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>483394</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>83542</xdr:rowOff>
+      <xdr:col>31</xdr:col>
+      <xdr:colOff>349448</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>128191</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -3309,7 +3453,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17015619" y="1286867"/>
+          <a:off x="16197064" y="617141"/>
           <a:ext cx="5375275" cy="2130425"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3356,7 +3500,7 @@
         <a:p>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000"/>
-            <a:t>・最大出現数・・・</a:t>
+            <a:t>・最大出現数　　　・・・</a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000"/>
@@ -3371,7 +3515,7 @@
         <a:p>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000"/>
-            <a:t>・作物の出現時間・・・</a:t>
+            <a:t>・作物の出現時間　・・・</a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000"/>
@@ -3386,7 +3530,7 @@
         <a:p>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000"/>
-            <a:t>・出現する作物・・・カブ</a:t>
+            <a:t>・出現する作物　　・・・カブ</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000"/>
         </a:p>
@@ -3808,9 +3952,9 @@
             <a:avLst/>
           </a:prstGeom>
           <a:solidFill>
-            <a:schemeClr val="tx1">
-              <a:lumMod val="65000"/>
-              <a:lumOff val="35000"/>
+            <a:schemeClr val="accent1">
+              <a:lumMod val="40000"/>
+              <a:lumOff val="60000"/>
             </a:schemeClr>
           </a:solidFill>
         </xdr:spPr>
@@ -4500,9 +4644,9 @@
             <a:avLst/>
           </a:prstGeom>
           <a:solidFill>
-            <a:schemeClr val="tx1">
-              <a:lumMod val="65000"/>
-              <a:lumOff val="35000"/>
+            <a:schemeClr val="accent1">
+              <a:lumMod val="40000"/>
+              <a:lumOff val="60000"/>
             </a:schemeClr>
           </a:solidFill>
         </xdr:spPr>
@@ -6828,6 +6972,696 @@
     </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>32579</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>6903</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>377860</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>168828</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="テキスト ボックス 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91C301A4-AC74-4481-AEBE-C3EFF8587CF6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1413014" y="7751142"/>
+          <a:ext cx="4486585" cy="631273"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3200"/>
+            <a:t>タイトル</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3200"/>
+            <a:t>UI</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>392044</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>7455</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>47107</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>169380</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="テキスト ボックス 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{91C301A4-AC74-4481-AEBE-C3EFF8587CF6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14886609" y="7751694"/>
+          <a:ext cx="4486585" cy="631273"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3200"/>
+            <a:t>ステージセレクト</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3200"/>
+            <a:t>UI</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>41966</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>14357</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>456097</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>193813</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="30" name="正方形/長方形 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E7CA8EE-68D2-E334-E57A-750B90D0E42A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1422401" y="8931966"/>
+          <a:ext cx="8696739" cy="4872934"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>318604</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>194364</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>289892</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>151848</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="31" name="テキスト ボックス 30">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9789D3A-D9E3-415C-939C-C09D80675EC9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5150126" y="11928060"/>
+          <a:ext cx="1351723" cy="426831"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+            <a:t>GameStart</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>305351</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>167309</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>276639</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>124792</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="32" name="テキスト ボックス 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9789D3A-D9E3-415C-939C-C09D80675EC9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5136873" y="12605026"/>
+          <a:ext cx="1351723" cy="426831"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+            <a:t>Exit</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>139699</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>112091</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>538370</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>69022</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="35" name="テキスト ボックス 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9789D3A-D9E3-415C-939C-C09D80675EC9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2900569" y="9968395"/>
+          <a:ext cx="5920410" cy="1130301"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="4000"/>
+            <a:t>Title</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>57424</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>195470</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>138044</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>165652</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="38" name="テキスト ボックス 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9789D3A-D9E3-415C-939C-C09D80675EC9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2818294" y="11459818"/>
+          <a:ext cx="1461054" cy="674204"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+            <a:t>Stage</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800" baseline="0"/>
+            <a:t> 1 Trophy</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>416888</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>16566</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>524564</xdr:colOff>
+      <xdr:row>53</xdr:row>
+      <xdr:rowOff>221423</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="41" name="テキスト ボックス 40">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9789D3A-D9E3-415C-939C-C09D80675EC9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7319062" y="11984936"/>
+          <a:ext cx="1488111" cy="674204"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+            <a:t>Stage</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800" baseline="0"/>
+            <a:t>2</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800" baseline="0"/>
+            <a:t>Trophy</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>58527</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>99945</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>166204</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>70127</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="42" name="テキスト ボックス 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9789D3A-D9E3-415C-939C-C09D80675EC9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2819397" y="12772336"/>
+          <a:ext cx="1488111" cy="674204"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+            <a:t>Stage</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800" baseline="0"/>
+            <a:t>3</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800" baseline="0"/>
+            <a:t>Trophy</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -8445,7 +9279,7 @@
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>8</a:t>
+            <a:t>7</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -9546,6 +10380,9 @@
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx1"/>
+        </a:solidFill>
       </xdr:spPr>
       <xdr:style>
         <a:lnRef idx="2">
@@ -9607,7 +10444,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="tx1"/>
+          <a:srgbClr val="C00000"/>
         </a:solidFill>
       </xdr:spPr>
       <xdr:style>
@@ -9673,7 +10510,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="tx1"/>
+          <a:srgbClr val="002060"/>
         </a:solidFill>
       </xdr:spPr>
       <xdr:style>
@@ -9739,7 +10576,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="tx1"/>
+          <a:srgbClr val="92D050"/>
         </a:solidFill>
       </xdr:spPr>
       <xdr:style>
@@ -9843,11 +10680,11 @@
       <xdr:col>5</xdr:col>
       <xdr:colOff>476006</xdr:colOff>
       <xdr:row>54</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:rowOff>26376</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>485775</xdr:colOff>
+      <xdr:colOff>479181</xdr:colOff>
       <xdr:row>55</xdr:row>
       <xdr:rowOff>66920</xdr:rowOff>
     </xdr:to>
@@ -9862,12 +10699,13 @@
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
           <a:stCxn id="15" idx="0"/>
+          <a:endCxn id="16" idx="2"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="3905006" y="12896850"/>
-          <a:ext cx="9769" cy="266945"/>
+          <a:off x="3891868" y="12796445"/>
+          <a:ext cx="3175" cy="277027"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -9898,15 +10736,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>431067</xdr:colOff>
+      <xdr:colOff>408842</xdr:colOff>
       <xdr:row>57</xdr:row>
-      <xdr:rowOff>34925</xdr:rowOff>
+      <xdr:rowOff>54709</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>68629</xdr:colOff>
+      <xdr:colOff>59104</xdr:colOff>
       <xdr:row>57</xdr:row>
-      <xdr:rowOff>40787</xdr:rowOff>
+      <xdr:rowOff>57151</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -9917,12 +10755,15 @@
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="15" idx="3"/>
+          <a:endCxn id="31" idx="1"/>
+        </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4545867" y="13608050"/>
-          <a:ext cx="323362" cy="5862"/>
+          <a:off x="4507876" y="13534226"/>
+          <a:ext cx="333435" cy="2442"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -10038,7 +10879,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="tx1"/>
+          <a:srgbClr val="C00000"/>
         </a:solidFill>
       </xdr:spPr>
       <xdr:style>
@@ -10074,15 +10915,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>431067</xdr:colOff>
+      <xdr:colOff>412017</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
+      <xdr:rowOff>38589</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>68629</xdr:colOff>
+      <xdr:colOff>70094</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>69362</xdr:rowOff>
+      <xdr:rowOff>38589</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -10093,12 +10934,15 @@
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="16" idx="3"/>
+          <a:endCxn id="30" idx="1"/>
+        </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4545867" y="12446000"/>
-          <a:ext cx="323362" cy="5862"/>
+          <a:off x="4511051" y="12335692"/>
+          <a:ext cx="341250" cy="0"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -10129,15 +10973,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>51044</xdr:colOff>
+      <xdr:colOff>70094</xdr:colOff>
       <xdr:row>50</xdr:row>
-      <xdr:rowOff>31750</xdr:rowOff>
+      <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>602517</xdr:colOff>
+      <xdr:colOff>621567</xdr:colOff>
       <xdr:row>54</xdr:row>
-      <xdr:rowOff>7326</xdr:rowOff>
+      <xdr:rowOff>26376</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -10152,14 +10996,14 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4851644" y="11938000"/>
+          <a:off x="4870694" y="11957050"/>
           <a:ext cx="1237273" cy="928076"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="tx1"/>
+          <a:srgbClr val="92D050"/>
         </a:solidFill>
       </xdr:spPr>
       <xdr:style>
@@ -10233,7 +11077,9 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="tx1"/>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
         </a:solidFill>
       </xdr:spPr>
       <xdr:style>
@@ -10299,7 +11145,9 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="tx1"/>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
         </a:solidFill>
       </xdr:spPr>
       <xdr:style>
@@ -10335,15 +11183,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>666750</xdr:colOff>
+      <xdr:colOff>676427</xdr:colOff>
       <xdr:row>59</xdr:row>
-      <xdr:rowOff>63500</xdr:rowOff>
+      <xdr:rowOff>44939</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>669192</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>2780</xdr:colOff>
       <xdr:row>60</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:rowOff>107462</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -10354,12 +11202,15 @@
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="31" idx="2"/>
+          <a:endCxn id="32" idx="0"/>
+        </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="5467350" y="14112875"/>
-          <a:ext cx="2442" cy="260350"/>
+        <a:xfrm>
+          <a:off x="5458634" y="13997422"/>
+          <a:ext cx="9525" cy="299006"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -10390,15 +11241,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>297229</xdr:colOff>
+      <xdr:colOff>264385</xdr:colOff>
       <xdr:row>55</xdr:row>
-      <xdr:rowOff>59837</xdr:rowOff>
+      <xdr:rowOff>66406</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>162902</xdr:colOff>
+      <xdr:colOff>130058</xdr:colOff>
       <xdr:row>59</xdr:row>
-      <xdr:rowOff>35414</xdr:rowOff>
+      <xdr:rowOff>41983</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -10413,14 +11264,14 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6469429" y="13156712"/>
-          <a:ext cx="1237273" cy="928077"/>
+          <a:off x="6412937" y="13072958"/>
+          <a:ext cx="1232018" cy="921508"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="tx1"/>
+          <a:srgbClr val="002060"/>
         </a:solidFill>
       </xdr:spPr>
       <xdr:style>
@@ -10456,15 +11307,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>650142</xdr:colOff>
+      <xdr:colOff>610577</xdr:colOff>
       <xdr:row>57</xdr:row>
-      <xdr:rowOff>34925</xdr:rowOff>
+      <xdr:rowOff>54195</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>287704</xdr:colOff>
+      <xdr:colOff>264385</xdr:colOff>
       <xdr:row>57</xdr:row>
-      <xdr:rowOff>40787</xdr:rowOff>
+      <xdr:rowOff>57151</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -10475,12 +11326,15 @@
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="31" idx="3"/>
+          <a:endCxn id="36" idx="1"/>
+        </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6136542" y="13608050"/>
-          <a:ext cx="323362" cy="5862"/>
+        <a:xfrm flipV="1">
+          <a:off x="6075956" y="13533712"/>
+          <a:ext cx="336981" cy="2956"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -10511,15 +11365,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>297229</xdr:colOff>
+      <xdr:colOff>251246</xdr:colOff>
       <xdr:row>50</xdr:row>
-      <xdr:rowOff>21737</xdr:rowOff>
+      <xdr:rowOff>48013</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>162902</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>235439</xdr:rowOff>
+      <xdr:colOff>116919</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>25232</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -10534,14 +11388,16 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6469429" y="11927987"/>
-          <a:ext cx="1237273" cy="928077"/>
+          <a:off x="6399798" y="11872151"/>
+          <a:ext cx="1232018" cy="923150"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="tx1"/>
+          <a:schemeClr val="accent4">
+            <a:lumMod val="75000"/>
+          </a:schemeClr>
         </a:solidFill>
       </xdr:spPr>
       <xdr:style>
@@ -10589,15 +11445,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>631092</xdr:colOff>
+      <xdr:colOff>621567</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>73025</xdr:rowOff>
+      <xdr:rowOff>36623</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>268654</xdr:colOff>
+      <xdr:colOff>251246</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>78887</xdr:rowOff>
+      <xdr:rowOff>38589</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -10608,12 +11464,15 @@
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="30" idx="3"/>
+          <a:endCxn id="38" idx="1"/>
+        </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6117492" y="12455525"/>
-          <a:ext cx="323362" cy="5862"/>
+        <a:xfrm flipV="1">
+          <a:off x="6086946" y="12333726"/>
+          <a:ext cx="312852" cy="1966"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -10644,15 +11503,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>456956</xdr:colOff>
+      <xdr:colOff>469833</xdr:colOff>
       <xdr:row>59</xdr:row>
-      <xdr:rowOff>47625</xdr:rowOff>
+      <xdr:rowOff>42497</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>466725</xdr:colOff>
+      <xdr:colOff>476006</xdr:colOff>
       <xdr:row>60</xdr:row>
-      <xdr:rowOff>76445</xdr:rowOff>
+      <xdr:rowOff>108119</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -10663,12 +11522,15 @@
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="41" idx="0"/>
+          <a:endCxn id="15" idx="2"/>
+        </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="3885956" y="14097000"/>
-          <a:ext cx="9769" cy="266945"/>
+          <a:off x="3885695" y="13994980"/>
+          <a:ext cx="6173" cy="302105"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -10699,15 +11561,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>582979</xdr:colOff>
+      <xdr:colOff>536996</xdr:colOff>
       <xdr:row>60</xdr:row>
-      <xdr:rowOff>88412</xdr:rowOff>
+      <xdr:rowOff>108119</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>448652</xdr:colOff>
+      <xdr:colOff>402669</xdr:colOff>
       <xdr:row>64</xdr:row>
-      <xdr:rowOff>63989</xdr:rowOff>
+      <xdr:rowOff>83696</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -10722,14 +11584,14 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3326179" y="14375912"/>
-          <a:ext cx="1237273" cy="928077"/>
+          <a:off x="3269686" y="14297085"/>
+          <a:ext cx="1232017" cy="921508"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="tx1"/>
+          <a:srgbClr val="0070C0"/>
         </a:solidFill>
       </xdr:spPr>
       <xdr:style>
@@ -10803,7 +11665,7 @@
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="tx1"/>
+          <a:srgbClr val="0070C0"/>
         </a:solidFill>
       </xdr:spPr>
       <xdr:style>
@@ -10902,15 +11764,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>657225</xdr:colOff>
+      <xdr:colOff>620102</xdr:colOff>
       <xdr:row>62</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:rowOff>95251</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>247650</xdr:colOff>
+      <xdr:colOff>326461</xdr:colOff>
       <xdr:row>62</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:rowOff>95908</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -10921,12 +11783,15 @@
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="48" idx="1"/>
+          <a:endCxn id="32" idx="3"/>
+        </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="6143625" y="14916150"/>
-          <a:ext cx="276225" cy="0"/>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="6085481" y="14757182"/>
+          <a:ext cx="389532" cy="657"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -10957,15 +11822,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>306754</xdr:colOff>
+      <xdr:colOff>326461</xdr:colOff>
       <xdr:row>60</xdr:row>
-      <xdr:rowOff>88412</xdr:rowOff>
+      <xdr:rowOff>108119</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>172427</xdr:colOff>
+      <xdr:colOff>192134</xdr:colOff>
       <xdr:row>64</xdr:row>
-      <xdr:rowOff>63989</xdr:rowOff>
+      <xdr:rowOff>83696</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -10980,14 +11845,16 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6478954" y="14375912"/>
-          <a:ext cx="1237273" cy="928077"/>
+          <a:off x="6475013" y="14297085"/>
+          <a:ext cx="1232018" cy="921508"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="tx1"/>
+          <a:schemeClr val="bg2">
+            <a:lumMod val="50000"/>
+          </a:schemeClr>
         </a:solidFill>
       </xdr:spPr>
       <xdr:style>
@@ -11289,7 +12156,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
@@ -11303,7 +12170,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70468DE0-FB43-4367-846C-C027C0DC19D2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
@@ -11317,7 +12184,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
@@ -11331,7 +12198,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
@@ -11345,7 +12212,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F6B105B-0976-477C-A343-44E7523407D9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="9" tint="0.59999389629810485"/>
   </sheetPr>
@@ -11359,7 +12226,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="8" tint="0.39997558519241921"/>
   </sheetPr>
@@ -11373,7 +12240,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="8" tint="0.39997558519241921"/>
   </sheetPr>
@@ -11387,7 +12254,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="8" tint="0.39997558519241921"/>
   </sheetPr>

--- a/FarmLife_仕様書.xlsx
+++ b/FarmLife_仕様書.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3"/>
+    <workbookView minimized="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="ゲームの動き" sheetId="1" r:id="rId1"/>
@@ -7662,6 +7662,371 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>373823</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>14909</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>97736</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>194365</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="43" name="正方形/長方形 42">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E7CA8EE-68D2-E334-E57A-750B90D0E42A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14868388" y="8932518"/>
+          <a:ext cx="8696739" cy="4872934"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>526773</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>112643</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>498061</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>70126</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="44" name="テキスト ボックス 43">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9789D3A-D9E3-415C-939C-C09D80675EC9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15021338" y="9030252"/>
+          <a:ext cx="1351723" cy="426831"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+            <a:t>Back</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>154607</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>2760</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>496957</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>27608</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="45" name="テキスト ボックス 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9789D3A-D9E3-415C-939C-C09D80675EC9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15339390" y="10563086"/>
+          <a:ext cx="1722784" cy="1667565"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+            <a:t>Stage</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800" baseline="0"/>
+            <a:t> 1</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>155158</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>224183</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>579783</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>14357</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="46" name="テキスト ボックス 45">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9789D3A-D9E3-415C-939C-C09D80675EC9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18100810" y="10549835"/>
+          <a:ext cx="1805060" cy="1667565"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+            <a:t>Stage</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800" baseline="0"/>
+            <a:t> 2</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>528430</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>210930</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>165652</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>1104</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="47" name="テキスト ボックス 46">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9789D3A-D9E3-415C-939C-C09D80675EC9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="21234952" y="10536582"/>
+          <a:ext cx="1707874" cy="1667565"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+            <a:t>Stage</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800" baseline="0"/>
+            <a:t> 3</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 

--- a/FarmLife_仕様書.xlsx
+++ b/FarmLife_仕様書.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GA3\Desktop\FarmLife\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GA3\Desktop\farmlife\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView minimized="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="ゲームの動き" sheetId="1" r:id="rId1"/>
@@ -11990,8 +11990,13 @@
           <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600"/>
-            <a:t>＋５</a:t>
-          </a:r>
+            <a:t>＋</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1600"/>
+            <a:t>1</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -12064,8 +12069,13 @@
           <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600"/>
-            <a:t>＋５</a:t>
-          </a:r>
+            <a:t>＋</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1600"/>
+            <a:t>1</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>

--- a/FarmLife_仕様書.xlsx
+++ b/FarmLife_仕様書.xlsx
@@ -30,9 +30,284 @@
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="42">
+  <si>
+    <t>耐久値+20</t>
+    <rPh sb="0" eb="3">
+      <t>タイキュウチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>耐久値+5</t>
+    <rPh sb="0" eb="3">
+      <t>タイキュウチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物追加ナス</t>
+  </si>
+  <si>
+    <t>出現数+3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>耐久値+10</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>耐久値+20</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出現数+5</t>
+    <rPh sb="0" eb="3">
+      <t>シュツゲンスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物追加ニンジン</t>
+    <rPh sb="0" eb="4">
+      <t>サクモツツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出現数+10</t>
+  </si>
+  <si>
+    <t>出現数+10</t>
+    <rPh sb="0" eb="3">
+      <t>シュツゲンスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出現時間+1/s</t>
+    <rPh sb="2" eb="4">
+      <t>ジカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出現時間+2/s</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出現時間+2/s</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃力+2</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃力+4</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>金額2倍</t>
+    <rPh sb="0" eb="2">
+      <t>キンガク</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>バイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃力+4</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃力+5</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃力+6</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出現数+10</t>
+    <rPh sb="0" eb="2">
+      <t>シュツゲン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>スウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物追加かぼちゃ</t>
+    <rPh sb="0" eb="2">
+      <t>サクモツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物追加キノコ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物追加金柿</t>
+    <rPh sb="4" eb="5">
+      <t>キン</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>カキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物追加金かぼ</t>
+    <rPh sb="4" eb="5">
+      <t>キン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>耐久値+25</t>
+  </si>
+  <si>
+    <t>耐久値+25</t>
+    <rPh sb="0" eb="3">
+      <t>タイキュウチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出現時間+3/s</t>
+    <rPh sb="0" eb="2">
+      <t>シュツゲン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出現時間+5/s</t>
+    <rPh sb="0" eb="2">
+      <t>シュツゲン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>耐久値+6</t>
+    <rPh sb="0" eb="3">
+      <t>タイキュウチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>耐久値+12</t>
+    <rPh sb="0" eb="3">
+      <t>タイキュウチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>耐久値+24</t>
+    <rPh sb="0" eb="3">
+      <t>タイキュウチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出現時間+5/s</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出現時間+7/s</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃力+8</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>金額3倍</t>
+    <rPh sb="0" eb="2">
+      <t>キンガク</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>バイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出現数+5</t>
+    <rPh sb="0" eb="2">
+      <t>シュツゲン</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>スウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出現数+10</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出現数+15</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物追加スイカ</t>
+    <rPh sb="0" eb="4">
+      <t>サクモツツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物追加金メロン</t>
+    <rPh sb="4" eb="5">
+      <t>キン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物追加きゅうり</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物追加金スイカ</t>
+    <rPh sb="4" eb="5">
+      <t>キン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -48,6 +323,14 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <family val="2"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -57,12 +340,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -71,8 +369,17 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -10715,275 +11022,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>610577</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>109903</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>571500</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>24423</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="正方形/長方形 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{78B7A9D2-AC9E-A1C4-1A8B-05341F3B6DD8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1296377" y="10825528"/>
-          <a:ext cx="6818923" cy="5391395"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="tx1"/>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>354135</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>61058</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>219807</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>36635</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="14" name="正方形/長方形 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{02F40E14-6C73-3D56-A307-D3E62A88B28E}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1721827" y="13493750"/>
-          <a:ext cx="1233365" cy="952500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="C00000"/>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600"/>
-            <a:t>攻撃力増加＋２</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>543169</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>66920</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>408842</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>42497</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="15" name="正方形/長方形 14">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{326E37B1-6E2F-4DFE-A5DE-844C31D73E53}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3278554" y="13499612"/>
-          <a:ext cx="1233365" cy="952500"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="002060"/>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600"/>
-            <a:t>耐久値増加＋１５</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>546344</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>50800</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>412017</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>26376</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="16" name="正方形/長方形 15">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3BBFD849-D744-42DB-9163-2B54ADB1A7C4}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3289544" y="11957050"/>
-          <a:ext cx="1237273" cy="928076"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="92D050"/>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600"/>
-            <a:t>作物追加</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1600"/>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600"/>
-            <a:t>ナス</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>4</xdr:col>
       <xdr:colOff>219807</xdr:colOff>
       <xdr:row>57</xdr:row>
@@ -11004,10 +11042,7 @@
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="14" idx="3"/>
-          <a:endCxn id="15" idx="1"/>
-        </xdr:cNvCxnSpPr>
+        <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
@@ -11043,539 +11078,31 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>476006</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>26376</xdr:rowOff>
+      <xdr:colOff>415404</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>42497</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
-      <xdr:colOff>479181</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>66920</xdr:rowOff>
+      <xdr:colOff>421577</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>108119</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="19" name="直線コネクタ 18">
+        <xdr:cNvPr id="40" name="直線コネクタ 39">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4DBB9B4A-DB1B-4B8D-9A74-9F3402E276AF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="15" idx="0"/>
-          <a:endCxn id="16" idx="2"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="3891868" y="12796445"/>
-          <a:ext cx="3175" cy="277027"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="76200">
-          <a:solidFill>
-            <a:schemeClr val="bg1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>408842</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>54709</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>59104</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>57151</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="25" name="直線コネクタ 24">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{850E13A1-4C38-4699-94FE-1F33712FB76F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="15" idx="3"/>
-          <a:endCxn id="31" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4507876" y="13534226"/>
-          <a:ext cx="333435" cy="2442"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="76200">
-          <a:solidFill>
-            <a:schemeClr val="bg1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>228600</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>44450</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>240567</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="26" name="直線コネクタ 25">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E8787067-07A3-4303-9D68-51A58E7EE423}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8555549E-EE6F-4040-828C-4BCCB65CA56B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr/>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="2286000" y="14093825"/>
-          <a:ext cx="11967" cy="307975"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="76200">
-          <a:solidFill>
-            <a:schemeClr val="bg1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>293077</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>111125</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>158749</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>86702</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="28" name="正方形/長方形 27">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{25321F07-198E-4F28-8E7F-AB7EDE86C1C5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1664677" y="14398625"/>
-          <a:ext cx="1237272" cy="928077"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="C00000"/>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600"/>
-            <a:t>攻撃力増加＋４</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>412017</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>38589</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>70094</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>38589</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="29" name="直線コネクタ 28">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98AF749A-B417-4A63-98D6-949C10A33D1F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="16" idx="3"/>
-          <a:endCxn id="30" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4511051" y="12335692"/>
-          <a:ext cx="341250" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="76200">
-          <a:solidFill>
-            <a:schemeClr val="bg1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>70094</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>50800</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>621567</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>26376</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="30" name="正方形/長方形 29">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0CF23385-C164-4C26-AC0E-A522B5569287}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4870694" y="11957050"/>
-          <a:ext cx="1237273" cy="928076"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="92D050"/>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600"/>
-            <a:t>作物追加</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1600"/>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600"/>
-            <a:t>ニンジン</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>59104</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>69362</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>610577</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>44939</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="31" name="正方形/長方形 30">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71627BDC-AEB3-41E5-A6C0-CF9016500E04}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4859704" y="13166237"/>
-          <a:ext cx="1237273" cy="928077"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg2">
-            <a:lumMod val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600"/>
-            <a:t>出現数増加＋５</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>68629</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>107462</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>620102</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>83039</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="32" name="正方形/長方形 31">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1E6CBB63-F8C6-4686-8703-959014EA35A7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4869229" y="14394962"/>
-          <a:ext cx="1237273" cy="928077"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg2">
-            <a:lumMod val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600"/>
-            <a:t>出現数増加＋１０</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>676427</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>44939</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>2780</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>107462</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="33" name="直線コネクタ 32">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F06AF8B6-99C3-4462-B54E-D460304FC7F9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="31" idx="2"/>
-          <a:endCxn id="32" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5458634" y="13997422"/>
-          <a:ext cx="9525" cy="299006"/>
+        <a:xfrm flipV="1">
+          <a:off x="3817190" y="14493283"/>
+          <a:ext cx="6173" cy="310550"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -11606,64 +11133,74 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>264385</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>66406</xdr:rowOff>
+      <xdr:colOff>1091046</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>51955</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>130058</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>41983</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>1444040</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>193313</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="36" name="正方形/長方形 35">
+        <xdr:cNvPr id="35" name="テキスト ボックス 34">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D9D1122-54F3-416D-90B3-DF378049B72C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33AB6622-0C52-40C6-AFF2-DC99CA50F0CA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvSpPr/>
+        <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6412937" y="13072958"/>
-          <a:ext cx="1232018" cy="921508"/>
+          <a:off x="14651182" y="9992591"/>
+          <a:ext cx="9393085" cy="626267"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:srgbClr val="002060"/>
+          <a:schemeClr val="lt1"/>
         </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
       </xdr:spPr>
       <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
         </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
+          <a:scrgbClr r="0" g="0" b="0"/>
         </a:effectRef>
         <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
+          <a:schemeClr val="dk1"/>
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600"/>
-            <a:t>耐久値増加＋２５</a:t>
-          </a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3200"/>
+            <a:t>Stage</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3200" baseline="0"/>
+            <a:t> 2</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3200"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -11671,592 +11208,75 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>610577</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>54195</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1285874</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>357188</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>264385</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>57151</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>138681</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>974796</xdr:rowOff>
     </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="37" name="直線コネクタ 36">
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="44" name="テキスト ボックス 43">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A3AF9CA-4791-4544-9039-30FF06C66FDD}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33AB6622-0C52-40C6-AFF2-DC99CA50F0CA}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="31" idx="3"/>
-          <a:endCxn id="36" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="6075956" y="13533712"/>
-          <a:ext cx="336981" cy="2956"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="76200">
-          <a:solidFill>
-            <a:schemeClr val="bg1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>251246</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>48013</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>116919</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>25232</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="38" name="正方形/長方形 37">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CD040DF9-08F3-4F64-8C69-521E30646B97}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
+        <xdr:cNvSpPr txBox="1"/>
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6399798" y="11872151"/>
-          <a:ext cx="1232018" cy="923150"/>
+          <a:off x="2786062" y="17502188"/>
+          <a:ext cx="9354119" cy="617608"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
         </a:prstGeom>
         <a:solidFill>
-          <a:schemeClr val="accent4">
-            <a:lumMod val="75000"/>
-          </a:schemeClr>
+          <a:schemeClr val="lt1"/>
         </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
       </xdr:spPr>
       <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
         </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
         </a:fillRef>
         <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
+          <a:scrgbClr r="0" g="0" b="0"/>
         </a:effectRef>
         <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
+          <a:schemeClr val="dk1"/>
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
         <a:lstStyle/>
         <a:p>
           <a:pPr algn="ctr"/>
           <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600"/>
-            <a:t>作物価値</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1600"/>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1600"/>
-            <a:t>×</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600"/>
-            <a:t>２</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>621567</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>36623</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>251246</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>38589</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="39" name="直線コネクタ 38">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5A7291A3-E235-4DE2-9139-A3AC219520D9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="30" idx="3"/>
-          <a:endCxn id="38" idx="1"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="6086946" y="12333726"/>
-          <a:ext cx="312852" cy="1966"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="76200">
-          <a:solidFill>
-            <a:schemeClr val="bg1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>469833</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>42497</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>476006</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>108119</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="40" name="直線コネクタ 39">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8555549E-EE6F-4040-828C-4BCCB65CA56B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="41" idx="0"/>
-          <a:endCxn id="15" idx="2"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="3885695" y="13994980"/>
-          <a:ext cx="6173" cy="302105"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="76200">
-          <a:solidFill>
-            <a:schemeClr val="bg1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>536996</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>108119</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>402669</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>83696</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="41" name="正方形/長方形 40">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C3F9B75-52F3-4CFA-9BF3-13DFA2D8A195}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="3269686" y="14297085"/>
-          <a:ext cx="1232017" cy="921508"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="0070C0"/>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600"/>
-            <a:t>出現時間</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1600"/>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600"/>
-            <a:t>＋</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1600"/>
-            <a:t>1</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>306754</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>59837</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>172427</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>35414</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="42" name="正方形/長方形 41">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FEB6A17E-4429-49EB-9C66-0A991EC1C2C3}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1678354" y="11966087"/>
-          <a:ext cx="1237273" cy="928077"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="0070C0"/>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600"/>
-            <a:t>出現時間</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1600"/>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600"/>
-            <a:t>＋</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1600"/>
-            <a:t>1</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>295031</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>304800</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>57395</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="43" name="直線コネクタ 42">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C634A1BF-9C4E-4F33-A2B2-DBA2A9FC42DA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipV="1">
-          <a:off x="2352431" y="12887325"/>
-          <a:ext cx="9769" cy="266945"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="76200">
-          <a:solidFill>
-            <a:schemeClr val="bg1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>620102</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>95251</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>326461</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>95908</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="46" name="直線コネクタ 45">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B37419BF-7F62-4CA9-BE37-BE6A1ADEFBB8}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="48" idx="1"/>
-          <a:endCxn id="32" idx="3"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1" flipV="1">
-          <a:off x="6085481" y="14757182"/>
-          <a:ext cx="389532" cy="657"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="76200">
-          <a:solidFill>
-            <a:schemeClr val="bg1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>326461</xdr:colOff>
-      <xdr:row>60</xdr:row>
-      <xdr:rowOff>108119</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>192134</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>83696</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="48" name="正方形/長方形 47">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D6DD4F7A-5767-4CF7-A65F-FF85CFA7A6F1}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6475013" y="14297085"/>
-          <a:ext cx="1232018" cy="921508"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="bg2">
-            <a:lumMod val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="15000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600"/>
-            <a:t>出現数増加＋１５</a:t>
-          </a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3200"/>
+            <a:t>Stage</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3200" baseline="0"/>
+            <a:t> 3</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3200"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -12633,11 +11653,207 @@
   <sheetPr>
     <tabColor theme="8" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
-  <sheetData/>
+  <dimension ref="C46:P65"/>
+  <sheetFormatPr defaultColWidth="19.75" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="46" spans="3:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="47" spans="3:16" s="1" customFormat="1" ht="97.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C47" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="F47" s="2"/>
+      <c r="G47" s="2"/>
+      <c r="K47" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="L47" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="M47" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="N47" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="O47" s="2"/>
+      <c r="P47" s="2"/>
+    </row>
+    <row r="48" spans="3:16" s="1" customFormat="1" ht="97.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C48" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M48" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="N48" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="O48" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="P48" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="49" spans="3:16" s="1" customFormat="1" ht="97.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C49" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F49" s="2"/>
+      <c r="G49" s="2"/>
+      <c r="K49" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M49" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="N49" s="2"/>
+      <c r="O49" s="2"/>
+      <c r="P49" s="2"/>
+    </row>
+    <row r="50" spans="3:16" s="1" customFormat="1" ht="97.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C50" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="K50" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="L50" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="M50" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N50" s="2"/>
+      <c r="O50" s="2"/>
+      <c r="P50" s="2"/>
+    </row>
+    <row r="51" spans="3:16" s="1" customFormat="1" ht="97.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="52" spans="3:16" s="1" customFormat="1" ht="97.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="53" spans="3:16" s="1" customFormat="1" ht="97.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="54" spans="3:16" ht="106.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C54" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F54" s="3"/>
+      <c r="G54" s="3"/>
+      <c r="H54" s="3"/>
+      <c r="I54" s="3"/>
+    </row>
+    <row r="55" spans="3:16" ht="106.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C55" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F55" s="3"/>
+      <c r="G55" s="3"/>
+      <c r="H55" s="3"/>
+      <c r="I55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" ht="106.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C56" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G56" s="3"/>
+      <c r="H56" s="3"/>
+      <c r="I56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" ht="106.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C57" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="58" spans="3:16" ht="106.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="59" spans="3:16" ht="106.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="60" spans="3:16" ht="106.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="61" spans="3:16" ht="106.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="62" spans="3:16" ht="106.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="63" spans="3:16" ht="106.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="64" spans="3:16" ht="106.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="65" ht="106.5" customHeight="1" x14ac:dyDescent="0.4"/>
+  </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/FarmLife_仕様書.xlsx
+++ b/FarmLife_仕様書.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="45">
   <si>
     <t>耐久値+20</t>
     <rPh sb="0" eb="3">
@@ -177,16 +177,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>作物追加金かぼ</t>
-    <rPh sb="4" eb="5">
-      <t>キン</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>耐久値+25</t>
-  </si>
-  <si>
     <t>耐久値+25</t>
     <rPh sb="0" eb="3">
       <t>タイキュウチ</t>
@@ -236,10 +226,6 @@
   </si>
   <si>
     <t>出現時間+5/s</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>出現時間+7/s</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -300,6 +286,48 @@
     <rPh sb="4" eb="5">
       <t>キン</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出現時間+5/s</t>
+    <rPh sb="0" eb="2">
+      <t>シュツゲン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>耐久値+25</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>耐久値+30</t>
+    <rPh sb="0" eb="3">
+      <t>タイキュウチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物追加金かぼちゃ</t>
+    <rPh sb="4" eb="5">
+      <t>キン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>耐久値+28</t>
+    <rPh sb="0" eb="2">
+      <t>タイキュウ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>チ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出現時間+7/s</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -11716,7 +11744,7 @@
         <v>22</v>
       </c>
       <c r="P48" s="2" t="s">
-        <v>23</v>
+        <v>42</v>
       </c>
     </row>
     <row r="49" spans="3:16" s="1" customFormat="1" ht="97.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
@@ -11735,12 +11763,14 @@
         <v>0</v>
       </c>
       <c r="L49" s="2" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>24</v>
+        <v>40</v>
       </c>
-      <c r="N49" s="2"/>
+      <c r="N49" s="2" t="s">
+        <v>41</v>
+      </c>
       <c r="O49" s="2"/>
       <c r="P49" s="2"/>
     </row>
@@ -11757,13 +11787,13 @@
       <c r="F50" s="2"/>
       <c r="G50" s="2"/>
       <c r="K50" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L50" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -11774,30 +11804,34 @@
     <row r="53" spans="3:16" s="1" customFormat="1" ht="97.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
     <row r="54" spans="3:16" ht="106.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="C54" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E54" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>29</v>
+      <c r="F54" s="3" t="s">
+        <v>43</v>
       </c>
-      <c r="E54" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F54" s="3"/>
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
     </row>
     <row r="55" spans="3:16" ht="106.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="C55" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>32</v>
+        <v>44</v>
       </c>
-      <c r="F55" s="3"/>
+      <c r="F55" s="3" t="s">
+        <v>39</v>
+      </c>
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
@@ -11810,10 +11844,10 @@
         <v>18</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
@@ -11821,25 +11855,25 @@
     </row>
     <row r="57" spans="3:16" ht="106.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="C57" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F57" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="D57" s="3" t="s">
+      <c r="G57" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="E57" s="3" t="s">
+      <c r="H57" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="F57" s="3" t="s">
+      <c r="I57" s="3" t="s">
         <v>38</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="58" spans="3:16" ht="106.5" customHeight="1" x14ac:dyDescent="0.4"/>

--- a/FarmLife_仕様書.xlsx
+++ b/FarmLife_仕様書.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="7"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="ゲームの動き" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="58">
   <si>
     <t>耐久値+20</t>
     <rPh sb="0" eb="3">
@@ -330,6 +330,142 @@
     <t>出現時間+7/s</t>
     <phoneticPr fontId="1"/>
   </si>
+  <si>
+    <t>作物出現数増加＋５</t>
+    <rPh sb="0" eb="2">
+      <t>サクモツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シュツゲン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>スウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物出現数増加＋１０</t>
+    <rPh sb="0" eb="7">
+      <t>サクモツシュツゲンスウゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物出現数増加＋５</t>
+    <rPh sb="0" eb="7">
+      <t>サクモツシュツゲンスウゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>制限時間追加＋５</t>
+    <rPh sb="0" eb="2">
+      <t>セイゲン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>制限時間追加＋３</t>
+    <rPh sb="0" eb="4">
+      <t>セイゲンジカン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>制限時間追加＋５</t>
+    <rPh sb="0" eb="4">
+      <t>セイゲンジカン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>制限時間追加＋１０</t>
+    <rPh sb="0" eb="4">
+      <t>セイゲンジカン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鍬の使用回数＋１０</t>
+    <rPh sb="0" eb="1">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カイスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鍬の使用回数＋１５</t>
+    <rPh sb="0" eb="1">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カイスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃力＋２</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>リョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃力＋４</t>
+    <rPh sb="0" eb="2">
+      <t>コウゲキ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>リョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃力＋６</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>金額倍化</t>
+    <rPh sb="0" eb="2">
+      <t>キンガク</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>バイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
 </sst>
 </file>
 
@@ -5978,16 +6114,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>441739</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>27607</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>115168</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>393</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>483151</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>27608</xdr:rowOff>
+      <xdr:col>5</xdr:col>
+      <xdr:colOff>156579</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>394</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -6002,8 +6138,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4583043" y="1904998"/>
-          <a:ext cx="2112065" cy="469349"/>
+          <a:off x="1475882" y="2449679"/>
+          <a:ext cx="2082483" cy="489858"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6135,6 +6271,10 @@
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
             <a:t>秒</a:t>
           </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -6249,8 +6389,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="14936856" y="1822727"/>
-          <a:ext cx="8696739" cy="4872934"/>
+          <a:off x="14729791" y="1894510"/>
+          <a:ext cx="8568556" cy="5088281"/>
           <a:chOff x="14936856" y="1822727"/>
           <a:chExt cx="8696739" cy="4872934"/>
         </a:xfrm>
@@ -6631,8 +6771,8 @@
           </xdr:nvSpPr>
           <xdr:spPr>
             <a:xfrm>
-              <a:off x="19161538" y="5068405"/>
-              <a:ext cx="1268895" cy="411922"/>
+              <a:off x="15625997" y="5094467"/>
+              <a:ext cx="1527321" cy="411922"/>
             </a:xfrm>
             <a:prstGeom prst="rect">
               <a:avLst/>
@@ -6728,66 +6868,6 @@
             </a:p>
           </xdr:txBody>
         </xdr:sp>
-        <xdr:sp macro="" textlink="">
-          <xdr:nvSpPr>
-            <xdr:cNvPr id="22" name="テキスト ボックス 21">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D507F669-4ACB-43F3-9FF7-F9A667621BE3}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvSpPr txBox="1"/>
-          </xdr:nvSpPr>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="18251003" y="1880153"/>
-              <a:ext cx="1861932" cy="480389"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-            <a:solidFill>
-              <a:schemeClr val="lt1"/>
-            </a:solidFill>
-            <a:ln w="9525" cmpd="sng">
-              <a:solidFill>
-                <a:schemeClr val="lt1">
-                  <a:shade val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
-            </a:ln>
-          </xdr:spPr>
-          <xdr:style>
-            <a:lnRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:lnRef>
-            <a:fillRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:fillRef>
-            <a:effectRef idx="0">
-              <a:scrgbClr r="0" g="0" b="0"/>
-            </a:effectRef>
-            <a:fontRef idx="minor">
-              <a:schemeClr val="dk1"/>
-            </a:fontRef>
-          </xdr:style>
-          <xdr:txBody>
-            <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:r>
-                <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
-                <a:t>鍬を購入　</a:t>
-              </a:r>
-              <a:r>
-                <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
-                <a:t>3G</a:t>
-              </a:r>
-              <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
-            </a:p>
-          </xdr:txBody>
-        </xdr:sp>
       </xdr:grpSp>
     </xdr:grpSp>
     <xdr:clientData/>
@@ -7181,134 +7261,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>552727</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>193814</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>36</xdr:col>
-      <xdr:colOff>621747</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>55219</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="39" name="テキスト ボックス 38">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56B55172-ED3D-4ACC-BD06-F92C88C2C43C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="20569031" y="897836"/>
-          <a:ext cx="4900542" cy="800100"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="38100" cmpd="sng">
-          <a:solidFill>
-            <a:srgbClr val="00B050"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600"/>
-            <a:t>鍬の耐久が最大じゃない時なら購入可能、その場合耐久は最大値まで回復</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1600"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>27</xdr:col>
-      <xdr:colOff>372717</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>193812</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>29</xdr:col>
-      <xdr:colOff>483705</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>27609</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="40" name="直線矢印コネクタ 39">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0B419F88-B85E-4ED4-9230-F59BA7BBBEBD}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="19008587" y="1367182"/>
-          <a:ext cx="1491422" cy="537818"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:schemeClr val="tx1">
-              <a:lumMod val="95000"/>
-              <a:lumOff val="5000"/>
-            </a:schemeClr>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>32579</xdr:colOff>
       <xdr:row>33</xdr:row>
@@ -7528,15 +7480,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>318604</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>194364</xdr:rowOff>
+      <xdr:colOff>328129</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>32439</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>289892</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>151848</xdr:rowOff>
+      <xdr:colOff>299417</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>228048</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -7551,8 +7503,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5150126" y="11928060"/>
-          <a:ext cx="1351723" cy="426831"/>
+          <a:off x="5128729" y="11462439"/>
+          <a:ext cx="1342888" cy="433734"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7745,270 +7697,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>57424</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>195470</xdr:rowOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>523502</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>28517</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>138044</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>165652</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="38" name="テキスト ボックス 37">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9789D3A-D9E3-415C-939C-C09D80675EC9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2818294" y="11459818"/>
-          <a:ext cx="1461054" cy="674204"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
-            <a:t>Stage</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800" baseline="0"/>
-            <a:t> 1 Trophy</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>416888</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>16566</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>524564</xdr:colOff>
-      <xdr:row>53</xdr:row>
-      <xdr:rowOff>221423</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="41" name="テキスト ボックス 40">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9789D3A-D9E3-415C-939C-C09D80675EC9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="7319062" y="11984936"/>
-          <a:ext cx="1488111" cy="674204"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
-            <a:t>Stage</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800" baseline="0"/>
-            <a:t>2</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800" baseline="0"/>
-            <a:t>Trophy</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>58527</xdr:colOff>
-      <xdr:row>54</xdr:row>
-      <xdr:rowOff>99945</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>166204</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>70127</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="42" name="テキスト ボックス 41">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9789D3A-D9E3-415C-939C-C09D80675EC9}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2819397" y="12772336"/>
-          <a:ext cx="1488111" cy="674204"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
-            <a:t>Stage</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800" baseline="0"/>
-            <a:t>3</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800" baseline="0"/>
-            <a:t>Trophy</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>373823</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>14909</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>97736</xdr:colOff>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>247415</xdr:colOff>
       <xdr:row>58</xdr:row>
-      <xdr:rowOff>194365</xdr:rowOff>
+      <xdr:rowOff>207973</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -8023,8 +7721,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14868388" y="8932518"/>
-          <a:ext cx="8696739" cy="4872934"/>
+          <a:off x="14130645" y="9335803"/>
+          <a:ext cx="8568556" cy="5078027"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8212,16 +7910,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>155158</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>224183</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>604195</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>6468</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>28</xdr:col>
-      <xdr:colOff>579783</xdr:colOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>348462</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>14357</xdr:rowOff>
+      <xdr:rowOff>41571</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -8236,8 +7934,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18100810" y="10549835"/>
-          <a:ext cx="1805060" cy="1667565"/>
+          <a:off x="16932766" y="11028254"/>
+          <a:ext cx="1785339" cy="1749603"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8288,16 +7986,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>30</xdr:col>
-      <xdr:colOff>528430</xdr:colOff>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>419572</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>210930</xdr:rowOff>
+      <xdr:rowOff>238144</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>165652</xdr:colOff>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>56795</xdr:colOff>
       <xdr:row>52</xdr:row>
-      <xdr:rowOff>1104</xdr:rowOff>
+      <xdr:rowOff>28318</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -8312,8 +8010,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21234952" y="10536582"/>
-          <a:ext cx="1707874" cy="1667565"/>
+          <a:off x="18789215" y="11015001"/>
+          <a:ext cx="1678294" cy="1749603"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8357,6 +8055,518 @@
             <a:t> 3</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>177366</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>240866</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>32</xdr:col>
+      <xdr:colOff>494945</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>31040</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="48" name="テキスト ボックス 47">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9789D3A-D9E3-415C-939C-C09D80675EC9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="20588080" y="11017723"/>
+          <a:ext cx="1678294" cy="1749603"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+            <a:t>Stage</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800" baseline="0"/>
+            <a:t> EX</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>328129</xdr:colOff>
+      <xdr:row>50</xdr:row>
+      <xdr:rowOff>194364</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>299417</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>151848</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="49" name="テキスト ボックス 48">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9789D3A-D9E3-415C-939C-C09D80675EC9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5128729" y="12100614"/>
+          <a:ext cx="1342888" cy="433734"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+            <a:t>Guide</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>653301</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>177247</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>248478</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>177248</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="50" name="テキスト ボックス 49">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9789D3A-D9E3-415C-939C-C09D80675EC9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7456872" y="6300461"/>
+          <a:ext cx="2316606" cy="489858"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
+            <a:t>鍬の耐久       </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+            <a:t>30/30</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>503464</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>41175</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>517070</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>41176</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="51" name="テキスト ボックス 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9789D3A-D9E3-415C-939C-C09D80675EC9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7307035" y="2490461"/>
+          <a:ext cx="2735035" cy="489858"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
+            <a:t>目標金額　　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+            <a:t>1234</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
+            <a:t>　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
+            <a:t>G</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>442291</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>180010</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>331769</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>120279</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="52" name="テキスト ボックス 51">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B978EEC7-4B76-4388-9630-83BAF1B2E0EE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14729791" y="1894510"/>
+          <a:ext cx="1250192" cy="430126"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
+            <a:t>パーク名</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>442291</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>180010</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>587292</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>122438</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="55" name="テキスト ボックス 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B978EEC7-4B76-4388-9630-83BAF1B2E0EE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14797026" y="1827275"/>
+          <a:ext cx="1512119" cy="413075"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
+            <a:t>パーク名</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>557893</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>204107</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>54428</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>163286</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="12" name="テキスト ボックス 11"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16886464" y="5347607"/>
+          <a:ext cx="1537607" cy="449036"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
+            <a:t>購入金額</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -9176,7 +9386,7 @@
           <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3200"/>
-            <a:t>ステージ毎の目標（仮）</a:t>
+            <a:t>ステージ毎のクリア条件</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -9268,15 +9478,7 @@
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
-            <a:t>800</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
-            <a:t>G</a:t>
+            <a:t>450G</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -9286,11 +9488,19 @@
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
-            <a:t>7</a:t>
+            <a:t>11</a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
             <a:t>分</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>40</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>秒</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
         </a:p>
@@ -9383,15 +9593,7 @@
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
-            <a:t>1900</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
-            <a:t>G</a:t>
+            <a:t>1200G</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -9401,11 +9603,19 @@
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
-            <a:t>9</a:t>
+            <a:t>18</a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
             <a:t>分</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>20</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>秒</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
         </a:p>
@@ -9498,7 +9708,7 @@
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
-            <a:t>3200</a:t>
+            <a:t>2400</a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
@@ -9516,7 +9726,122 @@
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
-            <a:t>12</a:t>
+            <a:t>20</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>分</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>371909</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>94817</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>458499</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>42862</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="テキスト ボックス 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18EB00FF-8029-42C2-A28D-B156A05B37C8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="18326534" y="8429192"/>
+          <a:ext cx="7682778" cy="1853045"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>Stage</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>EX</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>・目標金額・・・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>5400</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>G</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>・制限時間・・・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>25</a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
@@ -10086,16 +10411,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>366250</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>166534</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>56687</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>95096</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
-      <xdr:colOff>229213</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>106311</xdr:rowOff>
+      <xdr:colOff>610213</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>34873</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -10110,8 +10435,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14192863" y="6557502"/>
-          <a:ext cx="8850261" cy="1660422"/>
+          <a:off x="14558500" y="6524471"/>
+          <a:ext cx="8840276" cy="1606652"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10212,16 +10537,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>428932</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>219690</xdr:rowOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>119369</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>148252</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
-      <xdr:colOff>259940</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:colOff>640940</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>80962</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -10236,8 +10561,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14255545" y="6119045"/>
-          <a:ext cx="2596330" cy="424323"/>
+          <a:off x="14621182" y="6101377"/>
+          <a:ext cx="2593258" cy="408960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10350,6 +10675,2023 @@
             <a:t> 1</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>387007</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>227093</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="13" name="テキスト ボックス 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDE336B8-9C3D-4D5C-8E95-129D5022A397}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="24217313" y="2857500"/>
+          <a:ext cx="2411069" cy="703343"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3200"/>
+            <a:t>Stage</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3200" baseline="0"/>
+            <a:t> 2</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>571361</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>168993</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="テキスト ボックス 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0B26810-D22C-8324-4582-3A4B439131CA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="24217313" y="3810000"/>
+          <a:ext cx="2595423" cy="407118"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000"/>
+            <a:t>通常</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>/</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2000">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>爆発</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000"/>
+            <a:t>の作物</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>594992</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>9665</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>457955</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>191897</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="17" name="テキスト ボックス 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23E36173-4ABA-4DCB-9787-565F82BC66E5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="24074117" y="4295915"/>
+          <a:ext cx="8840276" cy="1610982"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・柿　　　             ・・・　価格　  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>10G</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>、作物の体力　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>5</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・かぼちゃ　　　・・・　価格　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>35</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>G</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>、作物の体力　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>12</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・キノコ　              ・・・　価格　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>48G</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>、作物の体力　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>18</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>650299</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>100446</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>481307</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>26984</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="18" name="テキスト ボックス 17">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0B26810-D22C-8324-4582-3A4B439131CA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="24129424" y="6053571"/>
+          <a:ext cx="2593258" cy="402788"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000"/>
+            <a:t>悪い作物</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>504938</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>110111</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>367901</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>49888</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="19" name="テキスト ボックス 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23E36173-4ABA-4DCB-9787-565F82BC66E5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="23984063" y="6539486"/>
+          <a:ext cx="8840276" cy="1606652"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・柿　　　             ・・・　価格　  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>-10G</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>、作物の体力　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>5</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・かぼちゃ　　　・・・　価格　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>-35</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>G</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>、作物の体力　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>12</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・キノコ　              ・・・　価格　 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>-48G</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>、作物の体力　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>18</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>508290</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>166255</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>38</xdr:col>
+      <xdr:colOff>339298</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>92793</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="テキスト ボックス 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0B26810-D22C-8324-4582-3A4B439131CA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="23987415" y="8262505"/>
+          <a:ext cx="2593258" cy="402788"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000"/>
+            <a:t>固有作物</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>466838</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>227875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>50</xdr:col>
+      <xdr:colOff>290079</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>167652</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="テキスト ボックス 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23E36173-4ABA-4DCB-9787-565F82BC66E5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="23945963" y="8800375"/>
+          <a:ext cx="10872241" cy="1606652"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・金の柿　　　             ・・・　価格　  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>50G</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>、作物の体力　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>10</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・金のかぼちゃ　　　・・・　価格　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>70</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>G</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>、作物の体力　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>18</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・ハロウィンかぼちゃ　              ・・・　価格　 </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>35G</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>、作物の体力　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>12</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>637713</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>223684</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>500676</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>163461</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="22" name="テキスト ボックス 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F71BC844-D82E-4E69-A591-9705989B4910}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14448963" y="8796184"/>
+          <a:ext cx="8840276" cy="1606652"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・金ニンジン　・・・　価格　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>40G</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>、作物の体力　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>12</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>9832</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>38715</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>531403</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>209550</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="23" name="テキスト ボックス 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23BA2181-81F2-462B-B624-DF8E02D041AA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14511645" y="8373090"/>
+          <a:ext cx="2593258" cy="408960"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000"/>
+            <a:t>固有作物</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>562128</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>52080</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>208782</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>36718</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="24" name="テキスト ボックス 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDE336B8-9C3D-4D5C-8E95-129D5022A397}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14373378" y="10767705"/>
+          <a:ext cx="2408904" cy="699013"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3200"/>
+            <a:t>Stage</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3200" baseline="0"/>
+            <a:t> 3</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>597155</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>4148</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>460118</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>166687</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="25" name="テキスト ボックス 24">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23E36173-4ABA-4DCB-9787-565F82BC66E5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14408405" y="12148523"/>
+          <a:ext cx="8840276" cy="1829414"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・メロン　　　・・・　価格　  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>30G</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>、作物の体力　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>12</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・スイカ　　　・・・　価格　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>60</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>G</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>、作物の体力　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>18</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・きゅうり　     ・・・　価格　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>110G</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>、作物の体力　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>20</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>659837</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>59147</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>490845</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>46461</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="テキスト ボックス 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0B26810-D22C-8324-4582-3A4B439131CA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14471087" y="11727272"/>
+          <a:ext cx="2593258" cy="463564"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000"/>
+            <a:t>通常</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>/</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2000">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>爆発</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000"/>
+            <a:t>の作物</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>675087</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>34455</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>538050</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>196994</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="テキスト ボックス 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23E36173-4ABA-4DCB-9787-565F82BC66E5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14529632" y="14824182"/>
+          <a:ext cx="8868418" cy="1859721"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・メロン　　　・・・　価格　  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>-30G</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>、作物の体力　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>12</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・スイカ　　　・・・　価格　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>-60</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>G</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>、作物の体力　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>18</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・きゅうり　     ・・・　価格　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>-110G</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>、作物の体力　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>20</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>45041</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>89454</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>568777</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>76768</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="28" name="テキスト ボックス 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0B26810-D22C-8324-4582-3A4B439131CA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14592314" y="14394272"/>
+          <a:ext cx="2601918" cy="472223"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000"/>
+            <a:t>悪い作物</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>463805</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>30991</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>326768</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>51955</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="29" name="テキスト ボックス 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23E36173-4ABA-4DCB-9787-565F82BC66E5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14318350" y="17245264"/>
+          <a:ext cx="8868418" cy="1475691"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・金メロン　　　・・・　価格　  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>200G</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>、作物の体力　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>20</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・金スイカ　　　・・・　価格　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>350</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>G</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>、作物の体力　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>30</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>526487</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>85990</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>357495</xdr:colOff>
+      <xdr:row>71</xdr:row>
+      <xdr:rowOff>73304</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="30" name="テキスト ボックス 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0B26810-D22C-8324-4582-3A4B439131CA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14381032" y="16815354"/>
+          <a:ext cx="2601918" cy="472223"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000"/>
+            <a:t>固有作物</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>428777</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>61605</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>75431</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>46243</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="33" name="テキスト ボックス 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDE336B8-9C3D-4D5C-8E95-129D5022A397}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="24598465" y="10777230"/>
+          <a:ext cx="2408904" cy="699013"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3200"/>
+            <a:t>Stage</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3200" baseline="0"/>
+            <a:t> EX</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>439992</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>13674</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>48</xdr:col>
+      <xdr:colOff>302956</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>149680</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="34" name="テキスト ボックス 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23E36173-4ABA-4DCB-9787-565F82BC66E5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="24252492" y="12505031"/>
+          <a:ext cx="8707607" cy="1115720"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・パイナップル　・・・ 価格      </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>25G</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>、作物の体力    </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>12</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・悪いパイナップル・・・価格　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>-25G</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>、作物の体力    </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>12</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>502674</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>68672</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>333682</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>55986</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="35" name="テキスト ボックス 34">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0B26810-D22C-8324-4582-3A4B439131CA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="24672362" y="11736797"/>
+          <a:ext cx="2593258" cy="463564"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000"/>
+            <a:t>作物</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>533290</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>211547</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>364298</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>198861</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="36" name="テキスト ボックス 35">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0B26810-D22C-8324-4582-3A4B439131CA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="24345790" y="13927547"/>
+          <a:ext cx="2552437" cy="477171"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000"/>
+            <a:t>特殊作物</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>524357</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>30002</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>48</xdr:col>
+      <xdr:colOff>387321</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="37" name="テキスト ボックス 36">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23E36173-4ABA-4DCB-9787-565F82BC66E5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="24336857" y="14970645"/>
+          <a:ext cx="8707607" cy="650355"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・冷たいパイナップル・・・価格</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>25G</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>、作物の体力    </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>12</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>659208</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>210331</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>44692</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>51954</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="38" name="テキスト ボックス 37">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A871A01B-3723-37E9-4BFF-091CBC9041CF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1351935" y="7726422"/>
+          <a:ext cx="11161848" cy="4205805"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>ステージ毎に特殊な作物がある</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・金の作物・・・通常の作物が金色でエフェクトを発している、通常の作物より少し硬いが入手できる金額は多くなる。</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・冷たい作物・・・通常の作物と見た目は変わらないが特殊なエフェクトを発している。採取するとお金を入手できるが体が冷えて、移動速度が低下する。</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>（</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>Stage EX</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>のみで出現）</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -10439,8 +12781,8 @@
       <xdr:rowOff>61057</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>207595</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>952500</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>24424</xdr:rowOff>
     </xdr:to>
@@ -10457,8 +12799,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1416537" y="1526442"/>
-          <a:ext cx="11100289" cy="1184520"/>
+          <a:off x="3096845" y="1432657"/>
+          <a:ext cx="11571655" cy="1106367"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10516,8 +12858,8 @@
       <xdr:rowOff>54708</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>659423</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>19</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
@@ -10534,8 +12876,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1397975" y="2985477"/>
-          <a:ext cx="14306063" cy="1654908"/>
+          <a:off x="3078283" y="2797908"/>
+          <a:ext cx="15209717" cy="1545492"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10669,13 +13011,13 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>5372</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>29797</xdr:rowOff>
+      <xdr:rowOff>76199</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>634512</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>1066800</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>201247</xdr:rowOff>
+      <xdr:rowOff>201246</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -10690,8 +13032,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1373064" y="5891335"/>
-          <a:ext cx="14306063" cy="659912"/>
+          <a:off x="3053372" y="5562599"/>
+          <a:ext cx="16301428" cy="582247"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10809,15 +13151,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>676517</xdr:colOff>
+      <xdr:colOff>1486142</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>139211</xdr:rowOff>
+      <xdr:rowOff>190499</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>561731</xdr:colOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>71438</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>66431</xdr:rowOff>
+      <xdr:rowOff>66430</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -10832,8 +13174,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1360363" y="7710365"/>
-          <a:ext cx="16981368" cy="659912"/>
+          <a:off x="2986330" y="7572374"/>
+          <a:ext cx="18087733" cy="590306"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -11303,6 +13645,82 @@
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3200" baseline="0"/>
             <a:t> 3</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>819150</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>342900</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>1172144</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>960508</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="テキスト ボックス 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33AB6622-0C52-40C6-AFF2-DC99CA50F0CA}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="15821025" y="17487900"/>
+          <a:ext cx="9354119" cy="617608"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3200"/>
+            <a:t>Stage</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3200" baseline="0"/>
+            <a:t> EX</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3200"/>
         </a:p>
@@ -11669,6 +14087,9 @@
   </sheetPr>
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="3" max="3" width="9" customWidth="1"/>
+  </cols>
   <sheetData/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11681,7 +14102,7 @@
   <sheetPr>
     <tabColor theme="8" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="C46:P65"/>
+  <dimension ref="C46:U65"/>
   <sheetFormatPr defaultColWidth="19.75" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
     <row r="46" spans="3:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
@@ -11747,7 +14168,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="49" spans="3:16" s="1" customFormat="1" ht="97.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="49" spans="3:21" s="1" customFormat="1" ht="97.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="C49" s="2" t="s">
         <v>10</v>
       </c>
@@ -11774,7 +14195,7 @@
       <c r="O49" s="2"/>
       <c r="P49" s="2"/>
     </row>
-    <row r="50" spans="3:16" s="1" customFormat="1" ht="97.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="50" spans="3:21" s="1" customFormat="1" ht="97.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="C50" s="2" t="s">
         <v>13</v>
       </c>
@@ -11799,10 +14220,10 @@
       <c r="O50" s="2"/>
       <c r="P50" s="2"/>
     </row>
-    <row r="51" spans="3:16" s="1" customFormat="1" ht="97.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="52" spans="3:16" s="1" customFormat="1" ht="97.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="53" spans="3:16" s="1" customFormat="1" ht="97.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="54" spans="3:16" ht="106.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="51" spans="3:21" s="1" customFormat="1" ht="97.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="52" spans="3:21" s="1" customFormat="1" ht="97.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="53" spans="3:21" s="1" customFormat="1" ht="97.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="54" spans="3:21" ht="106.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="C54" s="3" t="s">
         <v>26</v>
       </c>
@@ -11818,8 +14239,30 @@
       <c r="G54" s="3"/>
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
+      <c r="L54" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="N54" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="O54" s="3"/>
+      <c r="P54" s="3"/>
+      <c r="Q54" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="R54" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="S54" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="T54" s="3"/>
+      <c r="U54" s="3"/>
     </row>
-    <row r="55" spans="3:16" ht="106.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="55" spans="3:21" ht="106.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="C55" s="3" t="s">
         <v>24</v>
       </c>
@@ -11835,8 +14278,22 @@
       <c r="G55" s="3"/>
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
+      <c r="L55" s="3"/>
+      <c r="M55" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="N55" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+      <c r="S55" s="3"/>
+      <c r="T55" s="3"/>
+      <c r="U55" s="3"/>
     </row>
-    <row r="56" spans="3:16" ht="106.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="56" spans="3:21" ht="106.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="C56" s="3" t="s">
         <v>16</v>
       </c>
@@ -11852,8 +14309,32 @@
       <c r="G56" s="3"/>
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
+      <c r="L56" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="M56" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="N56" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="O56" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="P56" s="3"/>
+      <c r="Q56" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="R56" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="S56" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="T56" s="3"/>
+      <c r="U56" s="3"/>
     </row>
-    <row r="57" spans="3:16" ht="106.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="57" spans="3:21" ht="106.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="C57" s="3" t="s">
         <v>32</v>
       </c>
@@ -11875,14 +14356,28 @@
       <c r="I57" s="3" t="s">
         <v>38</v>
       </c>
+      <c r="L57" s="3"/>
+      <c r="M57" s="3"/>
+      <c r="N57" s="3"/>
+      <c r="O57" s="3"/>
+      <c r="P57" s="3"/>
+      <c r="Q57" s="3"/>
+      <c r="R57" s="3"/>
+      <c r="S57" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="T57" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="U57" s="3"/>
     </row>
-    <row r="58" spans="3:16" ht="106.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="59" spans="3:16" ht="106.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="60" spans="3:16" ht="106.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="61" spans="3:16" ht="106.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="62" spans="3:16" ht="106.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="63" spans="3:16" ht="106.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="64" spans="3:16" ht="106.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="58" spans="3:21" ht="106.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="59" spans="3:21" ht="106.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="60" spans="3:21" ht="106.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="61" spans="3:21" ht="106.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="62" spans="3:21" ht="106.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="63" spans="3:21" ht="106.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="64" spans="3:21" ht="106.5" customHeight="1" x14ac:dyDescent="0.4"/>
     <row r="65" ht="106.5" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <phoneticPr fontId="1"/>

--- a/FarmLife_仕様書.xlsx
+++ b/FarmLife_仕様書.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GA3\Desktop\farmlife\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GA3\Desktop\FarmLife\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="ゲームの動き" sheetId="1" r:id="rId1"/>
@@ -6282,14 +6282,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>552</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>295276</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>14356</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>276087</xdr:colOff>
+      <xdr:colOff>276088</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>14357</xdr:rowOff>
     </xdr:to>
@@ -6306,8 +6306,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7592943" y="1891747"/>
-          <a:ext cx="2346187" cy="469349"/>
+          <a:off x="7153276" y="1919356"/>
+          <a:ext cx="2724012" cy="476251"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6343,7 +6343,7 @@
         <a:p>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
-            <a:t>所持金　　</a:t>
+            <a:t>所持金　　　</a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
@@ -6389,8 +6389,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="14729791" y="1894510"/>
-          <a:ext cx="8568556" cy="5088281"/>
+          <a:off x="14944104" y="1846885"/>
+          <a:ext cx="8701225" cy="4945406"/>
           <a:chOff x="14936856" y="1822727"/>
           <a:chExt cx="8696739" cy="4872934"/>
         </a:xfrm>
@@ -7842,8 +7842,8 @@
     <xdr:to>
       <xdr:col>24</xdr:col>
       <xdr:colOff>496957</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>27608</xdr:rowOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>27215</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -7858,8 +7858,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15339390" y="10563086"/>
-          <a:ext cx="1722784" cy="1667565"/>
+          <a:off x="15122464" y="11024546"/>
+          <a:ext cx="1703064" cy="2473740"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -7918,8 +7918,8 @@
     <xdr:to>
       <xdr:col>27</xdr:col>
       <xdr:colOff>348462</xdr:colOff>
-      <xdr:row>52</xdr:row>
-      <xdr:rowOff>41571</xdr:rowOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>27215</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -7935,7 +7935,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="16932766" y="11028254"/>
-          <a:ext cx="1785339" cy="1749603"/>
+          <a:ext cx="1785339" cy="2470032"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -8289,15 +8289,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>503464</xdr:colOff>
+      <xdr:colOff>272142</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>41175</xdr:rowOff>
+      <xdr:rowOff>13961</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>517070</xdr:colOff>
+      <xdr:colOff>285748</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>41176</xdr:rowOff>
+      <xdr:rowOff>13962</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -8312,7 +8312,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7307035" y="2490461"/>
+          <a:off x="7075713" y="2463247"/>
           <a:ext cx="2735035" cy="489858"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -8362,146 +8362,6 @@
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
             <a:t>G</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>442291</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>180010</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>331769</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>120279</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="52" name="テキスト ボックス 51">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B978EEC7-4B76-4388-9630-83BAF1B2E0EE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14729791" y="1894510"/>
-          <a:ext cx="1250192" cy="430126"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
-            <a:t>パーク名</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>442291</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>180010</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>587292</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>122438</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="55" name="テキスト ボックス 54">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B978EEC7-4B76-4388-9630-83BAF1B2E0EE}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14797026" y="1827275"/>
-          <a:ext cx="1512119" cy="413075"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
-            <a:t>パーク名</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -8566,6 +8426,695 @@
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
             <a:t>購入金額</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>39656</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>153542</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>380999</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>111026</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="42" name="テキスト ボックス 41">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9789D3A-D9E3-415C-939C-C09D80675EC9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8203942" y="13869542"/>
+          <a:ext cx="1702057" cy="447341"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
+            <a:t>使用アセット</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>612321</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>231322</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>122464</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>176894</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="14" name="テキスト ボックス 13"/>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11498035" y="12967608"/>
+          <a:ext cx="2231572" cy="925286"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+            <a:t>ステージの番号とそのステージでの最高ランクが表示される</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>122464</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>231321</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>312964</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>204108</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="16" name="直線矢印コネクタ 15"/>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="14" idx="3"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm flipV="1">
+          <a:off x="13729607" y="12967607"/>
+          <a:ext cx="1551214" cy="462644"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="38100">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>82025</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>8659</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>43</xdr:col>
+      <xdr:colOff>403311</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>181214</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="53" name="テキスト ボックス 52">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{17FA805E-C2B7-486A-B7EF-BE242AFD34C7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="25712934" y="493568"/>
+          <a:ext cx="4477650" cy="657464"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3200"/>
+            <a:t>リザルト</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3200"/>
+            <a:t>UI</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3200"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>57827</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>124591</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>49</xdr:col>
+      <xdr:colOff>474467</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>69372</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="56" name="正方形/長方形 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9B5851A-E627-40E2-8F9E-EE5EECE57D77}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="25688736" y="1821773"/>
+          <a:ext cx="8729367" cy="5036326"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="tx2">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>41</xdr:col>
+      <xdr:colOff>373019</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>76100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>44</xdr:col>
+      <xdr:colOff>649826</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>76278</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="65" name="テキスト ボックス 64">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F95A7E08-905E-43CE-921D-D223F67A7889}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="28774837" y="6137464"/>
+          <a:ext cx="2354989" cy="485087"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
+            <a:t>タイトルに戻る</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>560055</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>141910</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>46</xdr:col>
+      <xdr:colOff>34636</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>225136</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="66" name="テキスト ボックス 65">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F95A7E08-905E-43CE-921D-D223F67A7889}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27576419" y="2081546"/>
+          <a:ext cx="4323672" cy="810590"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3200"/>
+            <a:t>ゲームクリア</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>121228</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>242355</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>45</xdr:col>
+      <xdr:colOff>412174</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>190501</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="67" name="テキスト ボックス 66">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F95A7E08-905E-43CE-921D-D223F67A7889}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27830319" y="3394264"/>
+          <a:ext cx="3754582" cy="433055"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600"/>
+            <a:t>クリアタイム</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>117764</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>204255</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>45</xdr:col>
+      <xdr:colOff>408710</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>152401</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="68" name="テキスト ボックス 67">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F95A7E08-905E-43CE-921D-D223F67A7889}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27826855" y="4083528"/>
+          <a:ext cx="3754582" cy="433055"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1600"/>
+            <a:t>採取回数</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>40</xdr:col>
+      <xdr:colOff>131619</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>27611</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>45</xdr:col>
+      <xdr:colOff>422565</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>207818</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="69" name="テキスト ボックス 68">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F95A7E08-905E-43CE-921D-D223F67A7889}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="27840710" y="5119156"/>
+          <a:ext cx="3754582" cy="665117"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2800"/>
+            <a:t>総合ランク</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -10118,15 +10667,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>290667</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>152399</xdr:rowOff>
+      <xdr:colOff>481167</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>190499</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>628651</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>137037</xdr:rowOff>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>133351</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>175137</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -10141,8 +10690,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14117280" y="1627238"/>
-          <a:ext cx="2411976" cy="722057"/>
+          <a:off x="14197167" y="419099"/>
+          <a:ext cx="2395384" cy="670438"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10188,15 +10737,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>367480</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>198489</xdr:rowOff>
+      <xdr:colOff>454071</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>129216</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>33</xdr:col>
-      <xdr:colOff>230443</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>138266</xdr:rowOff>
+      <xdr:colOff>317034</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>71436</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -10211,8 +10760,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14194093" y="4131392"/>
-          <a:ext cx="8850261" cy="1660422"/>
+          <a:off x="14265321" y="2510466"/>
+          <a:ext cx="8840276" cy="5419095"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10248,6 +10797,13 @@
         <a:p>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>通常・爆発する作物</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
             <a:t>・カブ　　　・・・　価格　  </a:t>
           </a:r>
           <a:r>
@@ -10307,77 +10863,9 @@
             <a:t>7</a:t>
           </a:r>
         </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>430162</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>15363</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>261170</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>184355</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="テキスト ボックス 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0B26810-D22C-8324-4582-3A4B439131CA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14256775" y="3702460"/>
-          <a:ext cx="2596330" cy="414798"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000"/>
-            <a:t>通常</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000">
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -10386,10 +10874,15 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>/</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2000">
+            <a:t>悪い作物</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="2400">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
               <a:solidFill>
                 <a:schemeClr val="dk1"/>
               </a:solidFill>
@@ -10398,208 +10891,250 @@
               <a:ea typeface="+mn-ea"/>
               <a:cs typeface="+mn-cs"/>
             </a:rPr>
-            <a:t>爆発</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000"/>
-            <a:t>の作物</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>56687</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>95096</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>610213</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>34873</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="テキスト ボックス 9">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F71BC844-D82E-4E69-A591-9705989B4910}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14558500" y="6524471"/>
-          <a:ext cx="8840276" cy="1606652"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
             <a:t>・カブ　　　・・・　価格　  </a:t>
           </a:r>
           <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
             <a:t>-2G</a:t>
           </a:r>
           <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
             <a:t>、作物の体力　</a:t>
           </a:r>
           <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
             <a:t>2</a:t>
           </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="2400">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
             <a:t>・ナス　　　・・・　価格　</a:t>
           </a:r>
           <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
             <a:t>  </a:t>
           </a:r>
           <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
             <a:t>-6</a:t>
           </a:r>
           <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
             <a:t>G</a:t>
           </a:r>
           <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
             <a:t>、作物の体力　</a:t>
           </a:r>
           <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
             <a:t>4</a:t>
           </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="2400">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
             <a:t>・ニンジン　・・・　価格　</a:t>
           </a:r>
           <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
             <a:t>-20G</a:t>
           </a:r>
           <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
             <a:t>、作物の体力　</a:t>
           </a:r>
           <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
             <a:t>6</a:t>
           </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>119369</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>148252</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>640940</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>80962</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="テキスト ボックス 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23BA2181-81F2-462B-B624-DF8E02D041AA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14621182" y="6101377"/>
-          <a:ext cx="2593258" cy="408960"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000"/>
-            <a:t>悪い作物</a:t>
-          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="2400">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>特殊な作物</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="2400">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>・金ニンジン　・・・　価格　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>40G</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>、作物の体力　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>12</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="2400">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -10608,15 +11143,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>427703</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>181896</xdr:rowOff>
+      <xdr:colOff>531612</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>112623</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
-      <xdr:colOff>74357</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>166534</xdr:rowOff>
+      <xdr:colOff>178266</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>97261</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -10631,8 +11166,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14254316" y="2885767"/>
-          <a:ext cx="2411976" cy="722057"/>
+          <a:off x="14386157" y="1567350"/>
+          <a:ext cx="2417564" cy="712002"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10682,16 +11217,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>309563</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>71438</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>387007</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>227093</xdr:rowOff>
+      <xdr:col>37</xdr:col>
+      <xdr:colOff>648944</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>60406</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -10706,7 +11241,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="24217313" y="2857500"/>
+          <a:off x="23788688" y="1500188"/>
           <a:ext cx="2411069" cy="703343"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -10759,784 +11294,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>571361</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>168993</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="14" name="テキスト ボックス 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0B26810-D22C-8324-4582-3A4B439131CA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="24217313" y="3810000"/>
-          <a:ext cx="2595423" cy="407118"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000"/>
-            <a:t>通常</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>/</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2000">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>爆発</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000"/>
-            <a:t>の作物</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>594992</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>9665</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>457955</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>191897</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="17" name="テキスト ボックス 16">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23E36173-4ABA-4DCB-9787-565F82BC66E5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="24074117" y="4295915"/>
-          <a:ext cx="8840276" cy="1610982"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>・柿　　　             ・・・　価格　  </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>10G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>5</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>・かぼちゃ　　　・・・　価格　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
-            <a:t>  </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
-            <a:t>35</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>12</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>・キノコ　              ・・・　価格　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>48G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>18</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>650299</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>100446</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>481307</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>26984</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="18" name="テキスト ボックス 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0B26810-D22C-8324-4582-3A4B439131CA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="24129424" y="6053571"/>
-          <a:ext cx="2593258" cy="402788"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000"/>
-            <a:t>悪い作物</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>504938</xdr:colOff>
-      <xdr:row>27</xdr:row>
-      <xdr:rowOff>110111</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>367901</xdr:colOff>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>466878</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>49888</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="19" name="テキスト ボックス 18">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23E36173-4ABA-4DCB-9787-565F82BC66E5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="23984063" y="6539486"/>
-          <a:ext cx="8840276" cy="1606652"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>・柿　　　             ・・・　価格　  </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>-10G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>5</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>・かぼちゃ　　　・・・　価格　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
-            <a:t>  </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
-            <a:t>-35</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>12</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>・キノコ　              ・・・　価格　 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>-48G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>18</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>508290</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>166255</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>38</xdr:col>
-      <xdr:colOff>339298</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>92793</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="20" name="テキスト ボックス 19">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0B26810-D22C-8324-4582-3A4B439131CA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="23987415" y="8262505"/>
-          <a:ext cx="2593258" cy="402788"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000"/>
-            <a:t>固有作物</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>466838</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>227875</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>50</xdr:col>
-      <xdr:colOff>290079</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>167652</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="21" name="テキスト ボックス 20">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23E36173-4ABA-4DCB-9787-565F82BC66E5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="23945963" y="8800375"/>
-          <a:ext cx="10872241" cy="1606652"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>・金の柿　　　             ・・・　価格　  </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>50G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>10</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>・金のかぼちゃ　　　・・・　価格　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
-            <a:t>  </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
-            <a:t>70</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>18</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>・ハロウィンかぼちゃ　              ・・・　価格　 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>35G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>12</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>637713</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>223684</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>500676</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>163461</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="22" name="テキスト ボックス 21">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F71BC844-D82E-4E69-A591-9705989B4910}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14448963" y="8796184"/>
-          <a:ext cx="8840276" cy="1606652"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>・金ニンジン　・・・　価格　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>40G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>12</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>9832</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>38715</xdr:rowOff>
+      <xdr:rowOff>28268</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>24</xdr:col>
-      <xdr:colOff>531403</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>209550</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="23" name="テキスト ボックス 22">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23BA2181-81F2-462B-B624-DF8E02D041AA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14511645" y="8373090"/>
-          <a:ext cx="2593258" cy="408960"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000"/>
-            <a:t>固有作物</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>562128</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>52080</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>208782</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>36718</xdr:rowOff>
+      <xdr:colOff>113532</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>12906</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -11551,7 +11318,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14373378" y="10767705"/>
+          <a:off x="14278128" y="8124518"/>
           <a:ext cx="2408904" cy="699013"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -11729,104 +11496,6 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>20</xdr:col>
-      <xdr:colOff>659837</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>59147</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>490845</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>46461</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="26" name="テキスト ボックス 25">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0B26810-D22C-8324-4582-3A4B439131CA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14471087" y="11727272"/>
-          <a:ext cx="2593258" cy="463564"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000"/>
-            <a:t>通常</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2000">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>/</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2000">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>爆発</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000"/>
-            <a:t>の作物</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>20</xdr:col>
       <xdr:colOff>675087</xdr:colOff>
       <xdr:row>61</xdr:row>
       <xdr:rowOff>34455</xdr:rowOff>
@@ -12692,6 +12361,995 @@
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
             <a:t>のみで出現）</a:t>
           </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>34</xdr:col>
+      <xdr:colOff>330678</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>101073</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>47</xdr:col>
+      <xdr:colOff>193641</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>204107</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="39" name="テキスト ボックス 38">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23E36173-4ABA-4DCB-9787-565F82BC66E5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="23462821" y="2550359"/>
+          <a:ext cx="8707606" cy="6226248"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>通常・爆発する作物</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・柿　　　              ・・・　価格　  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>10G</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>、作物の体力　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>5</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・かぼちゃ　　　・・・　価格　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>35</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>G</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>、作物の体力　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>12</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・キノコ　             ・・・　価格　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>48G</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>、作物の体力　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>18</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>悪い作物</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="2400">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>柿</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>　　　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>              </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>・・・　価格　  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>-10G</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>、作物の体力　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>5</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="2400">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>かぼちゃ</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>　　　・・・　価格　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>-35</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>G</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>、作物の体力　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>12</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="2400">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>キノコ</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>              </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>・・・　価格　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>-48G</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>、作物の体力　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>18</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="2400">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>特殊な作物</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="2400">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>・金</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>の柿</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>　・・・　価格　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>40G</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>、作物の体力　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>10</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="2400">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・金のかぼちゃ・・・価格　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>50G</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>、作物の体力　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>18</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・ハロウィンかぼちゃ・・・価格　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>70G</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>、作物の体力　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>12</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>511221</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>138742</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>33</xdr:col>
+      <xdr:colOff>374184</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="40" name="テキスト ボックス 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23E36173-4ABA-4DCB-9787-565F82BC66E5}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14322471" y="8949367"/>
+          <a:ext cx="8840276" cy="2480634"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>通常・爆発する作物</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・カブ　　　・・・　価格　  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>2G</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>、作物の体力　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>3</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・ナス　　　・・・　価格　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>6</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>G</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>、作物の体力　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>5</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・ニンジン　・・・　価格　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>20G</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>、作物の体力　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>7</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>悪い作物</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="2400">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>・カブ　　　・・・　価格　  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>-2G</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>、作物の体力　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>2</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="2400">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>・ナス　　　・・・　価格　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>  </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>-6</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>G</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>、作物の体力　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>4</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="2400">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>・ニンジン　・・・　価格　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>-20G</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>、作物の体力　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>6</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="2400">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>特殊な作物</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="2400">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>・金ニンジン　・・・　価格　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>40G</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>、作物の体力　</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
+              <a:solidFill>
+                <a:schemeClr val="dk1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>12</a:t>
+          </a:r>
+          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="2400">
+            <a:effectLst/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -14062,7 +14720,8 @@
   <sheetData/>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/FarmLife_仕様書.xlsx
+++ b/FarmLife_仕様書.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="ゲームの動き" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,8 @@
     <sheet name="UI" sheetId="8" r:id="rId5"/>
     <sheet name="ステージ" sheetId="7" r:id="rId6"/>
     <sheet name="作物" sheetId="5" r:id="rId7"/>
-    <sheet name="パーク" sheetId="6" r:id="rId8"/>
+    <sheet name="作物の種類" sheetId="10" r:id="rId8"/>
+    <sheet name="パーク" sheetId="6" r:id="rId9"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,438 +32,626 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="73">
   <si>
-    <t>耐久値+20</t>
-    <rPh sb="0" eb="3">
-      <t>タイキュウチ</t>
+    <t>Stage</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>名前</t>
+    <rPh sb="0" eb="2">
+      <t>ナマエ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>耐久値+5</t>
-    <rPh sb="0" eb="3">
-      <t>タイキュウチ</t>
+    <t>体力</t>
+    <rPh sb="0" eb="2">
+      <t>タイリョク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>作物追加ナス</t>
-  </si>
-  <si>
-    <t>出現数+3</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>耐久値+10</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>耐久値+20</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>出現数+5</t>
-    <rPh sb="0" eb="3">
-      <t>シュツゲンスウ</t>
+    <t>入手金額</t>
+    <rPh sb="0" eb="2">
+      <t>ニュウシュ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>キンガク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>作物追加ニンジン</t>
-    <rPh sb="0" eb="4">
-      <t>サクモツツイカ</t>
+    <t>メモ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>カブ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>最初から出現する作物</t>
+    <rPh sb="0" eb="2">
+      <t>サイショ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>シュツゲン</t>
+    </rPh>
+    <rPh sb="8" eb="10">
+      <t>サクモツ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>出現数+10</t>
-  </si>
-  <si>
-    <t>出現数+10</t>
-    <rPh sb="0" eb="3">
-      <t>シュツゲンスウ</t>
+    <t>悪いカブ</t>
+    <rPh sb="0" eb="1">
+      <t>ワル</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>出現時間+1/s</t>
-    <rPh sb="2" eb="4">
-      <t>ジカン</t>
+    <t>爆発するカブ</t>
+    <rPh sb="0" eb="2">
+      <t>バクハツ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>出現時間+2/s</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>出現時間+2/s</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>攻撃力+2</t>
-    <rPh sb="0" eb="3">
-      <t>コウゲキリョク</t>
+    <t>プレイヤーを吹き飛ばす</t>
+    <rPh sb="6" eb="7">
+      <t>フ</t>
+    </rPh>
+    <rPh sb="8" eb="9">
+      <t>ト</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>攻撃力+4</t>
+    <t>ナス</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>金額2倍</t>
-    <rPh sb="0" eb="2">
-      <t>キンガク</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>バイ</t>
+    <t>悪いナス</t>
+    <rPh sb="0" eb="1">
+      <t>ワル</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>攻撃力+4</t>
-    <rPh sb="0" eb="3">
-      <t>コウゲキリョク</t>
+    <t>爆発するナス</t>
+    <rPh sb="0" eb="2">
+      <t>バクハツ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>攻撃力+5</t>
-    <rPh sb="0" eb="3">
-      <t>コウゲキリョク</t>
+    <t>ニンジン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>悪いニンジン</t>
+    <rPh sb="0" eb="1">
+      <t>ワル</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>攻撃力+6</t>
-    <rPh sb="0" eb="3">
-      <t>コウゲキリョク</t>
+    <t>爆発するニンジン</t>
+    <rPh sb="0" eb="2">
+      <t>バクハツ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>出現数+10</t>
-    <rPh sb="0" eb="2">
-      <t>シュツゲン</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>スウ</t>
+    <t>金のニンジン</t>
+    <rPh sb="0" eb="1">
+      <t>キン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>作物追加かぼちゃ</t>
-    <rPh sb="0" eb="2">
-      <t>サクモツ</t>
+    <t>Stage１の中で最も単価が高い</t>
+    <rPh sb="7" eb="8">
+      <t>ナカ</t>
     </rPh>
-    <rPh sb="2" eb="4">
-      <t>ツイカ</t>
+    <rPh sb="9" eb="10">
+      <t>モット</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>タンカ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>タカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>作物追加キノコ</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>作物追加金柿</t>
-    <rPh sb="4" eb="5">
-      <t>キン</t>
-    </rPh>
-    <rPh sb="5" eb="6">
+    <t>柿</t>
+    <rPh sb="0" eb="1">
       <t>カキ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>耐久値+25</t>
-    <rPh sb="0" eb="3">
-      <t>タイキュウチ</t>
+    <t>悪い柿</t>
+    <rPh sb="0" eb="1">
+      <t>ワル</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>カキ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>出現時間+3/s</t>
+    <t>爆発する柿</t>
     <rPh sb="0" eb="2">
-      <t>シュツゲン</t>
+      <t>バクハツ</t>
     </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジカン</t>
+    <rPh sb="4" eb="5">
+      <t>カキ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>出現時間+5/s</t>
-    <rPh sb="0" eb="2">
-      <t>シュツゲン</t>
+    <t>金の柿</t>
+    <rPh sb="0" eb="1">
+      <t>キン</t>
     </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジカン</t>
+    <rPh sb="2" eb="3">
+      <t>カキ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>耐久値+6</t>
-    <rPh sb="0" eb="3">
-      <t>タイキュウチ</t>
+    <t>Stage6でも使用するので体力は低め</t>
+    <rPh sb="8" eb="10">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="14" eb="16">
+      <t>タイリョク</t>
+    </rPh>
+    <rPh sb="17" eb="18">
+      <t>ヒク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>耐久値+12</t>
-    <rPh sb="0" eb="3">
-      <t>タイキュウチ</t>
+    <t>かぼちゃ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ハロウィンかぼちゃ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>悪い作物と同等</t>
+    <rPh sb="0" eb="1">
+      <t>ワル</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>サクモツ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ドウトウ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>耐久値+24</t>
-    <rPh sb="0" eb="3">
-      <t>タイキュウチ</t>
+    <t>爆発するかぼちゃ</t>
+    <rPh sb="0" eb="2">
+      <t>バクハツ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>出現時間+5/s</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>攻撃力+8</t>
-    <rPh sb="0" eb="3">
-      <t>コウゲキリョク</t>
+    <t>一回り小さい</t>
+    <rPh sb="0" eb="2">
+      <t>ヒトマワ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>チイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>金額3倍</t>
-    <rPh sb="0" eb="2">
-      <t>キンガク</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>バイ</t>
+    <t>キノコ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>悪いキノコ</t>
+    <rPh sb="0" eb="1">
+      <t>ワル</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>出現数+5</t>
+    <t>爆発するキノコ</t>
     <rPh sb="0" eb="2">
-      <t>シュツゲン</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>スウ</t>
+      <t>バクハツ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>出現数+10</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>出現数+15</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>作物追加スイカ</t>
-    <rPh sb="0" eb="4">
-      <t>サクモツツイカ</t>
+    <t>サイズが小さい</t>
+    <rPh sb="4" eb="5">
+      <t>チイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>作物追加金メロン</t>
-    <rPh sb="4" eb="5">
+    <t>金のかぼちゃ</t>
+    <rPh sb="0" eb="1">
       <t>キン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>作物追加きゅうり</t>
+    <t>コスパは悪い</t>
+    <rPh sb="4" eb="5">
+      <t>ワル</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>作物追加金スイカ</t>
-    <rPh sb="4" eb="5">
+    <t>メロン</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>悪いメロン</t>
+    <rPh sb="0" eb="1">
+      <t>ワル</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>爆発するメロン</t>
+    <rPh sb="0" eb="2">
+      <t>バクハツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>少しだけ通常のものより値段が低い</t>
+    <rPh sb="0" eb="1">
+      <t>スコ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ツウジョウ</t>
+    </rPh>
+    <rPh sb="11" eb="13">
+      <t>ネダン</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ヒク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>乾燥したメロン</t>
+    <rPh sb="0" eb="2">
+      <t>カンソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>金のメロン</t>
+    <rPh sb="0" eb="1">
       <t>キン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>出現時間+5/s</t>
-    <rPh sb="0" eb="2">
-      <t>シュツゲン</t>
-    </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジカン</t>
+    <t>コスパがいい</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>スイカ</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>悪いスイカ</t>
+    <rPh sb="0" eb="1">
+      <t>ワル</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>耐久値+25</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>耐久値+30</t>
-    <rPh sb="0" eb="3">
-      <t>タイキュウチ</t>
+    <t>爆発するスイカ</t>
+    <rPh sb="0" eb="2">
+      <t>バクハツ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>作物追加金かぼちゃ</t>
-    <rPh sb="4" eb="5">
+    <t>単価が低くタイムロスにつながりやすい</t>
+    <rPh sb="0" eb="2">
+      <t>タンカ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヒク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>乾燥したスイカ</t>
+    <rPh sb="0" eb="2">
+      <t>カンソウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>体力が低く、誤爆しやすい</t>
+    <rPh sb="0" eb="2">
+      <t>タイリョク</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>ヒク</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>ゴバク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>金のスイカ</t>
+    <rPh sb="0" eb="1">
       <t>キン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>耐久値+28</t>
-    <rPh sb="0" eb="2">
-      <t>タイキュウ</t>
+    <t>実はメロンを取ったほうがいい</t>
+    <rPh sb="0" eb="1">
+      <t>ジツ</t>
     </rPh>
-    <rPh sb="2" eb="3">
-      <t>チ</t>
+    <rPh sb="6" eb="7">
+      <t>ト</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>出現時間+7/s</t>
+    <t>きゅうり</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>作物出現数増加＋５</t>
-    <rPh sb="0" eb="2">
-      <t>サクモツ</t>
+    <t>メロンの次に単価がいい</t>
+    <rPh sb="4" eb="5">
+      <t>ツギ</t>
     </rPh>
-    <rPh sb="2" eb="4">
-      <t>シュツゲン</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>スウ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>ゾウカ</t>
+    <rPh sb="6" eb="8">
+      <t>タンカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>作物出現数増加＋１０</t>
-    <rPh sb="0" eb="7">
-      <t>サクモツシュツゲンスウゾウカ</t>
+    <t>悪いきゅうり</t>
+    <rPh sb="0" eb="1">
+      <t>ワル</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>作物出現数増加＋５</t>
-    <rPh sb="0" eb="7">
-      <t>サクモツシュツゲンスウゾウカ</t>
+    <t>爆発するきゅうり</t>
+    <rPh sb="0" eb="2">
+      <t>バクハツ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>制限時間追加＋５</t>
+    <t>通常の作物と同じステータス</t>
     <rPh sb="0" eb="2">
-      <t>セイゲン</t>
+      <t>ツウジョウ</t>
     </rPh>
-    <rPh sb="2" eb="4">
-      <t>ジカン</t>
+    <rPh sb="3" eb="5">
+      <t>サクモツ</t>
     </rPh>
-    <rPh sb="4" eb="6">
-      <t>ツイカ</t>
+    <rPh sb="6" eb="7">
+      <t>オナ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>制限時間追加＋３</t>
-    <rPh sb="0" eb="4">
-      <t>セイゲンジカン</t>
+    <t>パイナップル</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>初期の状態ではこのステータスが限界</t>
+    <rPh sb="0" eb="2">
+      <t>ショキ</t>
     </rPh>
-    <rPh sb="4" eb="6">
-      <t>ツイカ</t>
+    <rPh sb="3" eb="5">
+      <t>ジョウタイ</t>
+    </rPh>
+    <rPh sb="15" eb="17">
+      <t>ゲンカイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>制限時間追加＋５</t>
-    <rPh sb="0" eb="4">
-      <t>セイゲンジカン</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ツイカ</t>
+    <t>悪いパイナップル</t>
+    <rPh sb="0" eb="1">
+      <t>ワル</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>制限時間追加＋１０</t>
-    <rPh sb="0" eb="4">
-      <t>セイゲンジカン</t>
-    </rPh>
-    <rPh sb="4" eb="6">
-      <t>ツイカ</t>
+    <t>凍ったパイナップル</t>
+    <rPh sb="0" eb="1">
+      <t>コオ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>鍬の使用回数＋１０</t>
-    <rPh sb="0" eb="1">
-      <t>クワ</t>
+    <t>移動速度が0.3fまで低下</t>
+    <rPh sb="0" eb="2">
+      <t>イドウ</t>
     </rPh>
     <rPh sb="2" eb="4">
-      <t>シヨウ</t>
+      <t>ソクド</t>
     </rPh>
-    <rPh sb="4" eb="6">
-      <t>カイスウ</t>
+    <rPh sb="11" eb="13">
+      <t>テイカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>鍬の使用回数＋１５</t>
-    <rPh sb="0" eb="1">
-      <t>クワ</t>
+    <t>移動速度が0.6fまで低下</t>
+    <rPh sb="0" eb="2">
+      <t>イドウ</t>
     </rPh>
     <rPh sb="2" eb="4">
-      <t>シヨウ</t>
+      <t>ソクド</t>
     </rPh>
-    <rPh sb="4" eb="6">
-      <t>カイスウ</t>
+    <rPh sb="11" eb="13">
+      <t>テイカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>攻撃力＋２</t>
+    <t>大根</t>
     <rPh sb="0" eb="2">
-      <t>コウゲキ</t>
-    </rPh>
-    <rPh sb="2" eb="3">
-      <t>リョク</t>
+      <t>ダイコン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>攻撃力＋４</t>
-    <rPh sb="0" eb="2">
-      <t>コウゲキ</t>
+    <t>悪い大根</t>
+    <rPh sb="0" eb="1">
+      <t>ワル</t>
     </rPh>
-    <rPh sb="2" eb="3">
-      <t>リョク</t>
+    <rPh sb="2" eb="4">
+      <t>ダイコン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>攻撃力＋６</t>
-    <rPh sb="0" eb="3">
-      <t>コウゲキリョク</t>
+    <t>爆発する大根</t>
+    <rPh sb="0" eb="2">
+      <t>バクハツ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ダイコン</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>金額倍化</t>
-    <rPh sb="0" eb="2">
-      <t>キンガク</t>
+    <t>凍った大根</t>
+    <rPh sb="0" eb="1">
+      <t>コオ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ダイコン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>金の大根</t>
+    <rPh sb="0" eb="1">
+      <t>キン</t>
     </rPh>
     <rPh sb="2" eb="4">
-      <t>バイカ</t>
+      <t>ダイコン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>青い魔法の作物</t>
+    <rPh sb="0" eb="1">
+      <t>アオ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サクモツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>悪い魔法の作物</t>
+    <rPh sb="0" eb="1">
+      <t>ワル</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>サクモツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>爆発する魔法の作物</t>
+    <rPh sb="0" eb="2">
+      <t>バクハツ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>サクモツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>乾燥した魔法の作物</t>
+    <rPh sb="0" eb="2">
+      <t>カンソウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>サクモツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>凍った魔法の作物</t>
+    <rPh sb="0" eb="1">
+      <t>コオ</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="6" eb="8">
+      <t>サクモツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>帯電した魔法の作物</t>
+    <rPh sb="0" eb="2">
+      <t>タイデン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>マホウ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>サクモツ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>移動速度が0.0fになり、移動できなくなる</t>
+    <rPh sb="0" eb="2">
+      <t>イドウ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ソクド</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>イドウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>色が変化しているので、すぐにわかる</t>
+    <rPh sb="0" eb="1">
+      <t>イロ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ヘンカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -504,27 +693,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color auto="1"/>
-      </left>
-      <right style="medium">
-        <color auto="1"/>
-      </right>
-      <top style="medium">
-        <color auto="1"/>
-      </top>
-      <bottom style="medium">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -533,17 +707,11 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1276,8 +1444,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="5185013" y="2231793"/>
-          <a:ext cx="84313" cy="354855"/>
+          <a:off x="5200701" y="2257006"/>
+          <a:ext cx="84313" cy="357657"/>
           <a:chOff x="5347658" y="2269252"/>
           <a:chExt cx="182704" cy="359018"/>
         </a:xfrm>
@@ -1666,7 +1834,7 @@
           <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-            <a:t>リザルト</a:t>
+            <a:t>タイトル</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1952,8 +2120,8 @@
     <xdr:to>
       <xdr:col>24</xdr:col>
       <xdr:colOff>247650</xdr:colOff>
-      <xdr:row>25</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1969,7 +2137,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="9149127" y="4727330"/>
-          <a:ext cx="7557723" cy="1254370"/>
+          <a:ext cx="7557723" cy="873370"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2023,14 +2191,6 @@
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
             <a:t>・ステージ毎に設定された制限時間を過ぎたら強制ゲームオーバー</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
-        </a:p>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1800"/>
-            <a:t>　制限時間は緩めに設定</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1800"/>
         </a:p>
@@ -2261,19 +2421,11 @@
         <a:p>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2800"/>
-            <a:t>ESC</a:t>
+            <a:t>ESC/TAB</a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2800"/>
-            <a:t>　　　　　　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2800" baseline="0"/>
-            <a:t>  　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2800"/>
-            <a:t>・・・設定</a:t>
+            <a:t>　　　　　　・・・一時停止</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2800"/>
         </a:p>
@@ -2807,8 +2959,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="5132387" y="3033910"/>
-          <a:ext cx="4094956" cy="4098925"/>
+          <a:off x="5102621" y="3115553"/>
+          <a:ext cx="4069443" cy="4214586"/>
           <a:chOff x="1381919" y="3108325"/>
           <a:chExt cx="4094956" cy="4098925"/>
         </a:xfrm>
@@ -3577,8 +3729,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="9538692" y="3716338"/>
-          <a:ext cx="8737402" cy="2311201"/>
+          <a:off x="9483413" y="3818392"/>
+          <a:ext cx="8682123" cy="2379236"/>
           <a:chOff x="14345841" y="3969345"/>
           <a:chExt cx="8737402" cy="2311201"/>
         </a:xfrm>
@@ -4397,8 +4549,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="4156581" y="5357135"/>
-          <a:ext cx="6925535" cy="4863414"/>
+          <a:off x="4202156" y="5544293"/>
+          <a:ext cx="7001491" cy="5042064"/>
           <a:chOff x="9030195" y="1657598"/>
           <a:chExt cx="6877792" cy="4886201"/>
         </a:xfrm>
@@ -4834,56 +4986,6 @@
           </a:p>
         </xdr:txBody>
       </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="22" name="正方形/長方形 21">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{39487164-1E1E-4D18-9FAA-9EA8557AD1F5}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="11577947" y="2090057"/>
-            <a:ext cx="841169" cy="890649"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:schemeClr val="bg1">
-              <a:lumMod val="65000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
       <xdr:cxnSp macro="">
         <xdr:nvCxnSpPr>
           <xdr:cNvPr id="23" name="直線コネクタ 22">
@@ -4899,46 +5001,6 @@
           <a:xfrm>
             <a:off x="12435940" y="4246914"/>
             <a:ext cx="915389" cy="0"/>
-          </a:xfrm>
-          <a:prstGeom prst="line">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln>
-            <a:solidFill>
-              <a:srgbClr val="FF0000"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-      </xdr:cxnSp>
-      <xdr:cxnSp macro="">
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="24" name="直線コネクタ 23">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D3CA600A-096E-4F02-88C1-0C534B447382}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvCxnSpPr/>
-        </xdr:nvCxnSpPr>
-        <xdr:spPr>
-          <a:xfrm flipV="1">
-            <a:off x="11969834" y="3005942"/>
-            <a:ext cx="4452" cy="799606"/>
           </a:xfrm>
           <a:prstGeom prst="line">
             <a:avLst/>
@@ -5089,8 +5151,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="14017798" y="5359140"/>
-          <a:ext cx="6925535" cy="4863414"/>
+          <a:off x="14169711" y="5546298"/>
+          <a:ext cx="7001493" cy="5042064"/>
           <a:chOff x="9030195" y="1657598"/>
           <a:chExt cx="6877792" cy="4886201"/>
         </a:xfrm>
@@ -5524,54 +5586,6 @@
           </a:p>
         </xdr:txBody>
       </xdr:sp>
-      <xdr:sp macro="" textlink="">
-        <xdr:nvSpPr>
-          <xdr:cNvPr id="56" name="正方形/長方形 55">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8CE7F05A-23CD-C948-771C-AA1155F01013}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvSpPr/>
-        </xdr:nvSpPr>
-        <xdr:spPr>
-          <a:xfrm>
-            <a:off x="11577947" y="2090057"/>
-            <a:ext cx="841169" cy="890649"/>
-          </a:xfrm>
-          <a:prstGeom prst="rect">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:solidFill>
-            <a:srgbClr val="92D050"/>
-          </a:solidFill>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="2">
-            <a:schemeClr val="accent1">
-              <a:shade val="15000"/>
-            </a:schemeClr>
-          </a:lnRef>
-          <a:fillRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="lt1"/>
-          </a:fontRef>
-        </xdr:style>
-        <xdr:txBody>
-          <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr algn="l"/>
-            <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-          </a:p>
-        </xdr:txBody>
-      </xdr:sp>
       <xdr:cxnSp macro="">
         <xdr:nvCxnSpPr>
           <xdr:cNvPr id="57" name="直線コネクタ 56">
@@ -5587,46 +5601,6 @@
           <a:xfrm>
             <a:off x="12435940" y="4246914"/>
             <a:ext cx="915389" cy="0"/>
-          </a:xfrm>
-          <a:prstGeom prst="line">
-            <a:avLst/>
-          </a:prstGeom>
-          <a:ln>
-            <a:solidFill>
-              <a:schemeClr val="bg1"/>
-            </a:solidFill>
-          </a:ln>
-        </xdr:spPr>
-        <xdr:style>
-          <a:lnRef idx="1">
-            <a:schemeClr val="accent1"/>
-          </a:lnRef>
-          <a:fillRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:fillRef>
-          <a:effectRef idx="0">
-            <a:schemeClr val="accent1"/>
-          </a:effectRef>
-          <a:fontRef idx="minor">
-            <a:schemeClr val="tx1"/>
-          </a:fontRef>
-        </xdr:style>
-      </xdr:cxnSp>
-      <xdr:cxnSp macro="">
-        <xdr:nvCxnSpPr>
-          <xdr:cNvPr id="58" name="直線コネクタ 57">
-            <a:extLst>
-              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A562902F-DE5B-7EC8-6E87-9728AF8C9D94}"/>
-              </a:ext>
-            </a:extLst>
-          </xdr:cNvPr>
-          <xdr:cNvCxnSpPr/>
-        </xdr:nvCxnSpPr>
-        <xdr:spPr>
-          <a:xfrm flipV="1">
-            <a:off x="11969834" y="3005942"/>
-            <a:ext cx="4452" cy="799606"/>
           </a:xfrm>
           <a:prstGeom prst="line">
             <a:avLst/>
@@ -9267,16 +9241,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>248883</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>58759</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>589062</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>17936</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>190498</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>69273</xdr:rowOff>
+      <xdr:colOff>122464</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>108856</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -9291,8 +9265,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7176156" y="4665395"/>
-          <a:ext cx="1327069" cy="980333"/>
+          <a:off x="6712276" y="3446936"/>
+          <a:ext cx="1574474" cy="1315563"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9404,7 +9378,7 @@
           <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3200"/>
-            <a:t>ステージの配置</a:t>
+            <a:t>ステージの簡易配置</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -9612,13 +9586,13 @@
       <xdr:col>15</xdr:col>
       <xdr:colOff>329046</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>155862</xdr:rowOff>
+      <xdr:rowOff>155861</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>1</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>17318</xdr:rowOff>
+      <xdr:col>26</xdr:col>
+      <xdr:colOff>204107</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>244927</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -9633,8 +9607,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="10719955" y="1853044"/>
-          <a:ext cx="5212773" cy="588819"/>
+          <a:off x="10534403" y="1870361"/>
+          <a:ext cx="7358990" cy="1313709"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9672,6 +9646,13 @@
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
             <a:t>畑に入ると、採取パートがスタート</a:t>
           </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>畑にもう一度出入りすると作物が再出現する</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -9680,15 +9661,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>311728</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>207818</xdr:rowOff>
+      <xdr:colOff>311729</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>77930</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>329046</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>86591</xdr:rowOff>
+      <xdr:rowOff>86592</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -9705,8 +9686,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="6546273" y="2147454"/>
-          <a:ext cx="4173682" cy="363682"/>
+          <a:off x="6434943" y="2527216"/>
+          <a:ext cx="4099460" cy="8662"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -9816,15 +9797,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>204355</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>15587</xdr:rowOff>
+      <xdr:colOff>136071</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>190500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>100446</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>221673</xdr:rowOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>14349</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -9840,9 +9821,9 @@
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm flipH="1">
-          <a:off x="8517082" y="4622223"/>
-          <a:ext cx="2667000" cy="448541"/>
+        <a:xfrm flipH="1" flipV="1">
+          <a:off x="8300357" y="4109357"/>
+          <a:ext cx="2685803" cy="558635"/>
         </a:xfrm>
         <a:prstGeom prst="straightConnector1">
           <a:avLst/>
@@ -9873,16 +9854,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>25</xdr:col>
-      <xdr:colOff>221673</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>31173</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>578861</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>102611</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>32</xdr:col>
-      <xdr:colOff>259772</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>177537</xdr:rowOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>616960</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>10850</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -9897,8 +9878,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="17539855" y="516082"/>
-          <a:ext cx="4887190" cy="631273"/>
+          <a:off x="1269424" y="7484486"/>
+          <a:ext cx="4872036" cy="622614"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9944,16 +9925,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>329046</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>103909</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>543359</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>199159</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>415636</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>51955</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>629949</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>166687</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -9968,8 +9949,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18339955" y="1801091"/>
-          <a:ext cx="7706590" cy="1887682"/>
+          <a:off x="543359" y="8295409"/>
+          <a:ext cx="7682778" cy="4730028"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10027,7 +10008,7 @@
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
-            <a:t>450G</a:t>
+            <a:t>600G</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -10037,7 +10018,7 @@
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
-            <a:t>11</a:t>
+            <a:t>16</a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
@@ -10051,7 +10032,134 @@
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
             <a:t>秒</a:t>
           </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>S</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>ランク・・・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>5</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>分</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>00</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>秒</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>A</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>ランク・・・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>10</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>分</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>00</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>秒</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>B</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>ランク・・・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>13</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>分</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>20</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>秒</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>C</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>ランク・・・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>16</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>分</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>40</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>秒</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -10059,16 +10167,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>342901</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>204354</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>80964</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>180540</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>429491</xdr:colOff>
-      <xdr:row>24</xdr:row>
-      <xdr:rowOff>152400</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>167554</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>214311</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -10083,8 +10191,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18353810" y="4083627"/>
-          <a:ext cx="7706590" cy="1887682"/>
+          <a:off x="8367714" y="8276790"/>
+          <a:ext cx="7682778" cy="4796271"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10142,7 +10250,7 @@
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
-            <a:t>1200G</a:t>
+            <a:t>1800G</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -10152,7 +10260,7 @@
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
-            <a:t>18</a:t>
+            <a:t>16</a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
@@ -10160,7 +10268,134 @@
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
-            <a:t>20</a:t>
+            <a:t>00</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>秒</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>S</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>ランク・・・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>4</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>分</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>48</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>秒</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>A</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>ランク・・・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>9</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>分</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>36</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>秒</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>B</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>ランク・・・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>12</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>分</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>40</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>秒</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>C</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>ランク・・・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>16</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>分</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>00</a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
@@ -10174,16 +10409,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>339437</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>148937</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>529937</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>29874</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>426027</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>96982</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>616527</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>166687</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -10198,8 +10433,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18350346" y="6452755"/>
-          <a:ext cx="7706590" cy="1887682"/>
+          <a:off x="529937" y="13126749"/>
+          <a:ext cx="7682778" cy="4661188"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10257,15 +10492,7 @@
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
-            <a:t>2400</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
-            <a:t>G</a:t>
+            <a:t>3200G</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -10280,6 +10507,141 @@
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
             <a:t>分</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>30</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>秒</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>S</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>ランク・・・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>6</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>分</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>9</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>秒</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>A</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>ランク・・・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>12</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>分</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>18</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>秒</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>B</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>ランク・・・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>16</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>分</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>24</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>秒</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>C</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>ランク・・・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>20</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>分</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>30</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>秒</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
         </a:p>
@@ -10289,16 +10651,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>371909</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>94817</xdr:rowOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>38534</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>71004</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>458499</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>42862</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>125124</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -10313,8 +10675,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="18326534" y="8429192"/>
-          <a:ext cx="7682778" cy="1853045"/>
+          <a:off x="8325284" y="13167879"/>
+          <a:ext cx="7682778" cy="4596246"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10362,7 +10724,7 @@
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
-            <a:t>EX</a:t>
+            <a:t>4</a:t>
           </a:r>
         </a:p>
         <a:p>
@@ -10372,7 +10734,7 @@
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
-            <a:t>5400</a:t>
+            <a:t>4600</a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
@@ -10390,13 +10752,635 @@
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
-            <a:t>25</a:t>
+            <a:t>22</a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
             <a:t>分</a:t>
           </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>30</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>秒</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>S</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>ランク・・・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>6</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>分</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>45</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>秒</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>A</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>ランク・・・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>13</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>分</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>30</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>秒</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>B</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>ランク・・・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>18</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>分</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>00</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>秒</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>C</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>ランク・・・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>22</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>分</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>30</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>秒</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>543544</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>186357</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>630134</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>78241</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="26" name="テキスト ボックス 25">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18EB00FF-8029-42C2-A28D-B156A05B37C8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="543544" y="18311071"/>
+          <a:ext cx="7570519" cy="4790456"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>Stage</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>5</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>・目標金額・・・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>5500G</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>・制限時間・・・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>23</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>分</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>20</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>秒</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>S</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>ランク・・・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>7</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>分</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>00</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>秒</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>A</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>ランク・・・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>14</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>分</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>00</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>秒</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>B</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>ランク・・・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>18</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>分</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>40</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>秒</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>C</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>ランク・・・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>23</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>分</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>20</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>秒</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>56408</xdr:colOff>
+      <xdr:row>74</xdr:row>
+      <xdr:rowOff>202686</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>142999</xdr:colOff>
+      <xdr:row>94</xdr:row>
+      <xdr:rowOff>94570</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="27" name="テキスト ボックス 26">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{18EB00FF-8029-42C2-A28D-B156A05B37C8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8220694" y="18327400"/>
+          <a:ext cx="7570519" cy="4790456"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>Stage</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>6</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>・目標金額・・・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>10000G</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>・制限時間・・・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>8</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>分</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>40</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>秒</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>S</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>ランク・・・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>2</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>分</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>36</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>秒</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>A</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>ランク・・・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>5</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>分</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>12</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>秒</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>B</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>ランク・・・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>6</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>分</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>56</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>秒</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>C</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>ランク・・・</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>8</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>分</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+            <a:t>40</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
+            <a:t>秒</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -10631,15 +11615,7 @@
         <a:p>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>・悪い作物・・・通常の作物よりも色が暗く、採取すると通常の作物の</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>1/2</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>の金額を失う。最低</a:t>
+            <a:t>・悪い作物・・・通常の作物よりも色が暗く、採取すると通常の作物と同量の金額を失う。最低</a:t>
           </a:r>
           <a:r>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
@@ -10657,7 +11633,7 @@
         <a:p>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>・爆発しそうな作物・・・通常の作物と見た目は変わらないがエフェクトがあり、採取してしまうとお金は得れるがプレイヤーが吹き飛んでタイムロスになる</a:t>
+            <a:t>・爆発しそうな作物・・・通常の作物と見た目は変わらないがエフェクトがあり、採取してしまうとお金は得れるがプレイヤーが吹き飛ぶ</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -10666,23 +11642,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>481167</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>190499</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>659208</xdr:colOff>
+      <xdr:row>31</xdr:row>
+      <xdr:rowOff>210331</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>133351</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>175137</xdr:rowOff>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>44692</xdr:colOff>
+      <xdr:row>66</xdr:row>
+      <xdr:rowOff>225136</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="テキスト ボックス 5">
+        <xdr:cNvPr id="38" name="テキスト ボックス 37">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26037DCB-E75D-4B86-8A2A-B13DDBD2B97F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A871A01B-3723-37E9-4BFF-091CBC9041CF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -10690,8 +11666,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14197167" y="419099"/>
-          <a:ext cx="2395384" cy="670438"/>
+          <a:off x="1351935" y="7726422"/>
+          <a:ext cx="11161848" cy="8500714"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10726,1606 +11702,6 @@
         <a:lstStyle/>
         <a:p>
           <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3200"/>
-            <a:t>作物の種類</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>454071</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>129216</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>317034</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>71436</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="テキスト ボックス 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23E36173-4ABA-4DCB-9787-565F82BC66E5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14265321" y="2510466"/>
-          <a:ext cx="8840276" cy="5419095"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>通常・爆発する作物</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>・カブ　　　・・・　価格　  </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>2G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>3</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>・ナス　　　・・・　価格　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
-            <a:t>  </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
-            <a:t>6</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>5</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>・ニンジン　・・・　価格　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>20G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>7</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>悪い作物</a:t>
-          </a:r>
-          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="2400">
-            <a:effectLst/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>・カブ　　　・・・　価格　  </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>-2G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>2</a:t>
-          </a:r>
-          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="2400">
-            <a:effectLst/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>・ナス　　　・・・　価格　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>  </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>-6</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>4</a:t>
-          </a:r>
-          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="2400">
-            <a:effectLst/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>・ニンジン　・・・　価格　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>-20G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>6</a:t>
-          </a:r>
-          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="2400">
-            <a:effectLst/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>特殊な作物</a:t>
-          </a:r>
-          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="2400">
-            <a:effectLst/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>・金ニンジン　・・・　価格　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>40G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>12</a:t>
-          </a:r>
-          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="2400">
-            <a:effectLst/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>531612</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>112623</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>178266</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>97261</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="テキスト ボックス 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDE336B8-9C3D-4D5C-8E95-129D5022A397}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14386157" y="1567350"/>
-          <a:ext cx="2417564" cy="712002"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3200"/>
-            <a:t>Stage</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3200" baseline="0"/>
-            <a:t> 1</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3200"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>309563</xdr:colOff>
-      <xdr:row>6</xdr:row>
-      <xdr:rowOff>71438</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>37</xdr:col>
-      <xdr:colOff>648944</xdr:colOff>
-      <xdr:row>9</xdr:row>
-      <xdr:rowOff>60406</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="13" name="テキスト ボックス 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDE336B8-9C3D-4D5C-8E95-129D5022A397}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="23788688" y="1500188"/>
-          <a:ext cx="2411069" cy="703343"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3200"/>
-            <a:t>Stage</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3200" baseline="0"/>
-            <a:t> 2</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3200"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>466878</xdr:colOff>
-      <xdr:row>34</xdr:row>
-      <xdr:rowOff>28268</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>113532</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>12906</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="24" name="テキスト ボックス 23">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDE336B8-9C3D-4D5C-8E95-129D5022A397}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14278128" y="8124518"/>
-          <a:ext cx="2408904" cy="699013"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3200"/>
-            <a:t>Stage</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3200" baseline="0"/>
-            <a:t> 3</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3200"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>597155</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>4148</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>460118</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>166687</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="25" name="テキスト ボックス 24">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23E36173-4ABA-4DCB-9787-565F82BC66E5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14408405" y="12148523"/>
-          <a:ext cx="8840276" cy="1829414"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>・メロン　　　・・・　価格　  </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>30G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>12</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>・スイカ　　　・・・　価格　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
-            <a:t>  </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
-            <a:t>60</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>18</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>・きゅうり　     ・・・　価格　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>110G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>20</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>675087</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>34455</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>538050</xdr:colOff>
-      <xdr:row>68</xdr:row>
-      <xdr:rowOff>196994</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="27" name="テキスト ボックス 26">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23E36173-4ABA-4DCB-9787-565F82BC66E5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14529632" y="14824182"/>
-          <a:ext cx="8868418" cy="1859721"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>・メロン　　　・・・　価格　  </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>-30G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>12</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>・スイカ　　　・・・　価格　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
-            <a:t>  </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
-            <a:t>-60</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>18</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>・きゅうり　     ・・・　価格　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>-110G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>20</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>45041</xdr:colOff>
-      <xdr:row>59</xdr:row>
-      <xdr:rowOff>89454</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>568777</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>76768</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="28" name="テキスト ボックス 27">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0B26810-D22C-8324-4582-3A4B439131CA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14592314" y="14394272"/>
-          <a:ext cx="2601918" cy="472223"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000"/>
-            <a:t>悪い作物</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>463805</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>30991</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>326768</xdr:colOff>
-      <xdr:row>77</xdr:row>
-      <xdr:rowOff>51955</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="29" name="テキスト ボックス 28">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23E36173-4ABA-4DCB-9787-565F82BC66E5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14318350" y="17245264"/>
-          <a:ext cx="8868418" cy="1475691"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>・金メロン　　　・・・　価格　  </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>200G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>20</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>・金スイカ　　　・・・　価格　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
-            <a:t>  </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
-            <a:t>350</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>30</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>526487</xdr:colOff>
-      <xdr:row>69</xdr:row>
-      <xdr:rowOff>85990</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>357495</xdr:colOff>
-      <xdr:row>71</xdr:row>
-      <xdr:rowOff>73304</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="30" name="テキスト ボックス 29">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0B26810-D22C-8324-4582-3A4B439131CA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14381032" y="16815354"/>
-          <a:ext cx="2601918" cy="472223"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000"/>
-            <a:t>固有作物</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>428777</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>61605</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>39</xdr:col>
-      <xdr:colOff>75431</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>46243</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="33" name="テキスト ボックス 32">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DDE336B8-9C3D-4D5C-8E95-129D5022A397}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="24598465" y="10777230"/>
-          <a:ext cx="2408904" cy="699013"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3200"/>
-            <a:t>Stage</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3200" baseline="0"/>
-            <a:t> EX</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3200"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>439992</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>13674</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>48</xdr:col>
-      <xdr:colOff>302956</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>149680</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="34" name="テキスト ボックス 33">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23E36173-4ABA-4DCB-9787-565F82BC66E5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="24252492" y="12505031"/>
-          <a:ext cx="8707607" cy="1115720"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>・パイナップル　・・・ 価格      </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>25G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>、作物の体力    </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>12</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>・悪いパイナップル・・・価格　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>-25G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>、作物の体力    </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>12</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>502674</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>68672</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>39</xdr:col>
-      <xdr:colOff>333682</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>55986</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="35" name="テキスト ボックス 34">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0B26810-D22C-8324-4582-3A4B439131CA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="24672362" y="11736797"/>
-          <a:ext cx="2593258" cy="463564"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000"/>
-            <a:t>作物</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>533290</xdr:colOff>
-      <xdr:row>56</xdr:row>
-      <xdr:rowOff>211547</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>39</xdr:col>
-      <xdr:colOff>364298</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>198861</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="36" name="テキスト ボックス 35">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0B26810-D22C-8324-4582-3A4B439131CA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="24345790" y="13927547"/>
-          <a:ext cx="2552437" cy="477171"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2000"/>
-            <a:t>特殊作物</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>35</xdr:col>
-      <xdr:colOff>524357</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>30002</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>48</xdr:col>
-      <xdr:colOff>387321</xdr:colOff>
-      <xdr:row>63</xdr:row>
-      <xdr:rowOff>190500</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="37" name="テキスト ボックス 36">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23E36173-4ABA-4DCB-9787-565F82BC66E5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="24336857" y="14970645"/>
-          <a:ext cx="8707607" cy="650355"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>・冷たいパイナップル・・・価格</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>25G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>、作物の体力    </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>12</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>659208</xdr:colOff>
-      <xdr:row>31</xdr:row>
-      <xdr:rowOff>210331</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>18</xdr:col>
-      <xdr:colOff>44692</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>51954</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="38" name="テキスト ボックス 37">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A871A01B-3723-37E9-4BFF-091CBC9041CF}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1351935" y="7726422"/>
-          <a:ext cx="11161848" cy="4205805"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
             <a:t>ステージ毎に特殊な作物がある</a:t>
           </a:r>
@@ -12344,6 +11720,31 @@
         <a:p>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・乾燥した作物・・・見た目は同じだが特殊なエフェクトを発し、採取すると</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>移動速度が</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+            <a:t>0.6f</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>、あで低下する。</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
             <a:t>・冷たい作物・・・通常の作物と見た目は変わらないが特殊なエフェクトを発している。採取するとお金を入手できるが体が冷えて、移動速度が低下する。</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
@@ -12361,994 +11762,16 @@
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
             <a:t>のみで出現）</a:t>
           </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>34</xdr:col>
-      <xdr:colOff>330678</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>101073</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>47</xdr:col>
-      <xdr:colOff>193641</xdr:colOff>
-      <xdr:row>35</xdr:row>
-      <xdr:rowOff>204107</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="39" name="テキスト ボックス 38">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23E36173-4ABA-4DCB-9787-565F82BC66E5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="23462821" y="2550359"/>
-          <a:ext cx="8707606" cy="6226248"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+        </a:p>
         <a:p>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>通常・爆発する作物</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>・柿　　　              ・・・　価格　  </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>10G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>5</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>・かぼちゃ　　　・・・　価格　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
-            <a:t>  </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
-            <a:t>35</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>12</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>・キノコ　             ・・・　価格　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>48G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>18</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>悪い作物</a:t>
-          </a:r>
-          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="2400">
-            <a:effectLst/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>・</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>柿</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>　　　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>              </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>・・・　価格　  </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>-10G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>5</a:t>
-          </a:r>
-          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="2400">
-            <a:effectLst/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>・</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>かぼちゃ</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>　　　・・・　価格　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>  </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>-35</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>12</a:t>
-          </a:r>
-          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="2400">
-            <a:effectLst/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>・</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>キノコ</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>              </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>・・・　価格　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>-48G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>18</a:t>
-          </a:r>
-          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="2400">
-            <a:effectLst/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>特殊な作物</a:t>
-          </a:r>
-          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="2400">
-            <a:effectLst/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>・金</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>の柿</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>　・・・　価格　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>40G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>10</a:t>
-          </a:r>
-          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="2400">
-            <a:effectLst/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>・金のかぼちゃ・・・価格　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>50G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>18</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>・ハロウィンかぼちゃ・・・価格　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>70G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>12</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>511221</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>138742</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>33</xdr:col>
-      <xdr:colOff>374184</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>1</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="40" name="テキスト ボックス 39">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{23E36173-4ABA-4DCB-9787-565F82BC66E5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="14322471" y="8949367"/>
-          <a:ext cx="8840276" cy="2480634"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>通常・爆発する作物</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>・カブ　　　・・・　価格　  </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>2G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>3</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>・ナス　　　・・・　価格　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400" baseline="0"/>
-            <a:t>  </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0"/>
-            <a:t>6</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>5</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>・ニンジン　・・・　価格　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>20G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>7</a:t>
-          </a:r>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>悪い作物</a:t>
-          </a:r>
-          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="2400">
-            <a:effectLst/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>・カブ　　　・・・　価格　  </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>-2G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>2</a:t>
-          </a:r>
-          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="2400">
-            <a:effectLst/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>・ナス　　　・・・　価格　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>  </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>-6</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>4</a:t>
-          </a:r>
-          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="2400">
-            <a:effectLst/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>・ニンジン　・・・　価格　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>-20G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>6</a:t>
-          </a:r>
-          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="2400">
-            <a:effectLst/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>特殊な作物</a:t>
-          </a:r>
-          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="2400">
-            <a:effectLst/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>・金ニンジン　・・・　価格　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>40G</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>、作物の体力　</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:rPr>
-            <a:t>12</a:t>
-          </a:r>
-          <a:endParaRPr lang="ja-JP" altLang="ja-JP" sz="2400">
-            <a:effectLst/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
+            <a:t>・びりびりしてる作物・・・特殊なエフェクトがあり、採取するとお金は入手できるが感電してその場で停止してしまう。</a:t>
+          </a:r>
           <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
         </a:p>
       </xdr:txBody>
@@ -13519,7 +11942,7 @@
       <xdr:col>12</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>123265</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -13534,8 +11957,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3078283" y="2797908"/>
-          <a:ext cx="15209717" cy="1545492"/>
+          <a:off x="3033459" y="2878590"/>
+          <a:ext cx="14985600" cy="1715822"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -13869,238 +12292,12 @@
         <a:p>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>・作物価値</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>2</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>倍・・・作物の価値を</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>2</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>倍にする。一つの作物から得られる金額が多くなるが、悪い作物の金額も</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
-            <a:t>2</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
-            <a:t>倍になる</a:t>
+            <a:t>・作物価値倍化・・・作物の価値を指定した倍数にする。一つの作物から得られる金額が多くなるが、悪い作物の金額も倍になる</a:t>
           </a:r>
           <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>352994</xdr:colOff>
-      <xdr:row>39</xdr:row>
-      <xdr:rowOff>141357</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="テキスト ボックス 10">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A33FB063-C390-4987-9C29-BDDDD7B151FD}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1367692" y="9036538"/>
-          <a:ext cx="4456071" cy="629819"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3200"/>
-            <a:t>パーク簡易配置図</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>35426</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>27713</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>388420</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>169071</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="テキスト ボックス 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33AB6622-0C52-40C6-AFF2-DC99CA50F0CA}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1403118" y="10041175"/>
-          <a:ext cx="4456071" cy="629819"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:schemeClr val="lt1"/>
-        </a:solidFill>
-        <a:ln w="9525" cmpd="sng">
-          <a:solidFill>
-            <a:schemeClr val="lt1">
-              <a:shade val="50000"/>
-            </a:schemeClr>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="dk1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3200"/>
-            <a:t>Stage</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3200" baseline="0"/>
-            <a:t> 1</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3200"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>219807</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>48846</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>543169</xdr:colOff>
-      <xdr:row>57</xdr:row>
-      <xdr:rowOff>54708</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="18" name="直線コネクタ 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E7B22A46-9C4F-EA0B-C328-E7F1F13216B0}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2955192" y="13970000"/>
-          <a:ext cx="323362" cy="5862"/>
-        </a:xfrm>
-        <a:prstGeom prst="line">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="76200">
-          <a:solidFill>
-            <a:schemeClr val="bg1"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
@@ -14160,23 +12357,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>1091046</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>51955</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1439918</xdr:colOff>
+      <xdr:row>35</xdr:row>
+      <xdr:rowOff>86844</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>1444040</xdr:colOff>
-      <xdr:row>43</xdr:row>
-      <xdr:rowOff>193313</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>25214</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>198099</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="35" name="テキスト ボックス 34">
+        <xdr:cNvPr id="16" name="テキスト ボックス 15">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33AB6622-0C52-40C6-AFF2-DC99CA50F0CA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53D3CB20-6294-41F8-84E5-D35588206D5F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14184,8 +12381,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="14651182" y="9992591"/>
-          <a:ext cx="9393085" cy="626267"/>
+          <a:off x="2941506" y="8323168"/>
+          <a:ext cx="18105943" cy="581902"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -14216,19 +12413,14 @@
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3200"/>
-            <a:t>Stage</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3200" baseline="0"/>
-            <a:t> 2</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3200"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・爆発耐性・・・爆発する作物を採取しても、吹き飛ばなくなる</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -14237,22 +12429,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>1285874</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>357188</xdr:rowOff>
+      <xdr:colOff>1491466</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>138392</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>138681</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>974796</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>76762</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>14323</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="44" name="テキスト ボックス 43">
+        <xdr:cNvPr id="17" name="テキスト ボックス 16">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33AB6622-0C52-40C6-AFF2-DC99CA50F0CA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53D3CB20-6294-41F8-84E5-D35588206D5F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14260,8 +12452,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="2786062" y="17502188"/>
-          <a:ext cx="9354119" cy="617608"/>
+          <a:off x="2993054" y="9080686"/>
+          <a:ext cx="18105943" cy="581902"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -14292,19 +12484,14 @@
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3200"/>
-            <a:t>Stage</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3200" baseline="0"/>
-            <a:t> 3</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3200"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・毒耐性・・・悪い作物でも金額が通常の作物と同じように増える</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -14312,23 +12499,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>819150</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>342900</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1486984</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>201144</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>16</xdr:col>
-      <xdr:colOff>1172144</xdr:colOff>
-      <xdr:row>51</xdr:row>
-      <xdr:rowOff>960508</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>72280</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>77076</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="15" name="テキスト ボックス 14">
+        <xdr:cNvPr id="19" name="テキスト ボックス 18">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{33AB6622-0C52-40C6-AFF2-DC99CA50F0CA}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53D3CB20-6294-41F8-84E5-D35588206D5F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -14336,8 +12523,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15821025" y="17487900"/>
-          <a:ext cx="9354119" cy="617608"/>
+          <a:off x="2988572" y="9849409"/>
+          <a:ext cx="18105943" cy="581902"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -14368,19 +12555,156 @@
         </a:fontRef>
       </xdr:style>
       <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="ctr"/>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
         <a:lstStyle/>
         <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3200"/>
-            <a:t>Stage</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="3200" baseline="0"/>
-            <a:t> EX</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="3200"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・砂塵耐性・・・乾燥した作物を採取しても移動速度が低下しない</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1482501</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>39780</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>67797</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>38976</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="20" name="テキスト ボックス 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53D3CB20-6294-41F8-84E5-D35588206D5F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2984089" y="10629339"/>
+          <a:ext cx="18105943" cy="581902"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・凍結耐性・・・凍った作物を採取しても移動速度が低下しない</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>54872</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>12886</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>141756</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>56906</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="21" name="テキスト ボックス 20">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53D3CB20-6294-41F8-84E5-D35588206D5F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="3058048" y="11364445"/>
+          <a:ext cx="18105943" cy="581902"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="lt1"/>
+        </a:solidFill>
+        <a:ln w="9525" cmpd="sng">
+          <a:solidFill>
+            <a:schemeClr val="lt1">
+              <a:shade val="50000"/>
+            </a:schemeClr>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="dk1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="2400"/>
+            <a:t>・麻痺耐性・・・帯電した作物を採取しても移動速度が低下しない</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="2400"/>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -14759,285 +13083,810 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
+    <tabColor theme="4" tint="0.39997558519241921"/>
+  </sheetPr>
+  <dimension ref="A1:E53"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
+  <cols>
+    <col min="1" max="1" width="20.75" customWidth="1"/>
+    <col min="2" max="2" width="22.875" customWidth="1"/>
+    <col min="3" max="3" width="26.875" customWidth="1"/>
+    <col min="4" max="4" width="26.75" customWidth="1"/>
+    <col min="5" max="5" width="43.75" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A5">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>5</v>
+      </c>
+      <c r="D5">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A6">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+      <c r="D6">
+        <v>-6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A7">
+        <v>1</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A8">
+        <v>1</v>
+      </c>
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8">
+        <v>7</v>
+      </c>
+      <c r="D8">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A9">
+        <v>1</v>
+      </c>
+      <c r="B9" t="s">
+        <v>14</v>
+      </c>
+      <c r="C9">
+        <v>7</v>
+      </c>
+      <c r="D9">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A10">
+        <v>1</v>
+      </c>
+      <c r="B10" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10">
+        <v>7</v>
+      </c>
+      <c r="D10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A11">
+        <v>1</v>
+      </c>
+      <c r="B11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C11">
+        <v>12</v>
+      </c>
+      <c r="D11">
+        <v>45</v>
+      </c>
+      <c r="E11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A13">
+        <v>2</v>
+      </c>
+      <c r="B13" t="s">
+        <v>18</v>
+      </c>
+      <c r="C13">
+        <v>5</v>
+      </c>
+      <c r="D13">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A14">
+        <v>2</v>
+      </c>
+      <c r="B14" t="s">
+        <v>19</v>
+      </c>
+      <c r="C14">
+        <v>5</v>
+      </c>
+      <c r="D14">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A15">
+        <v>2</v>
+      </c>
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15">
+        <v>5</v>
+      </c>
+      <c r="D15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A16">
+        <v>2</v>
+      </c>
+      <c r="B16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C16">
+        <v>8</v>
+      </c>
+      <c r="D16">
+        <v>60</v>
+      </c>
+      <c r="E16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A17">
+        <v>2</v>
+      </c>
+      <c r="B17" t="s">
+        <v>23</v>
+      </c>
+      <c r="C17">
+        <v>12</v>
+      </c>
+      <c r="D17">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A18">
+        <v>2</v>
+      </c>
+      <c r="B18" t="s">
+        <v>24</v>
+      </c>
+      <c r="C18">
+        <v>12</v>
+      </c>
+      <c r="D18">
+        <v>-25</v>
+      </c>
+      <c r="E18" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A19">
+        <v>2</v>
+      </c>
+      <c r="B19" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19">
+        <v>12</v>
+      </c>
+      <c r="D19">
+        <v>25</v>
+      </c>
+      <c r="E19" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A20">
+        <v>2</v>
+      </c>
+      <c r="B20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20">
+        <v>16</v>
+      </c>
+      <c r="D20">
+        <v>70</v>
+      </c>
+      <c r="E20" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A21">
+        <v>2</v>
+      </c>
+      <c r="B21" t="s">
+        <v>28</v>
+      </c>
+      <c r="C21">
+        <v>10</v>
+      </c>
+      <c r="D21">
+        <v>40</v>
+      </c>
+      <c r="E21" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A22">
+        <v>2</v>
+      </c>
+      <c r="B22" t="s">
+        <v>29</v>
+      </c>
+      <c r="C22">
+        <v>10</v>
+      </c>
+      <c r="D22">
+        <v>-40</v>
+      </c>
+      <c r="E22" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A23">
+        <v>2</v>
+      </c>
+      <c r="B23" t="s">
+        <v>30</v>
+      </c>
+      <c r="C23">
+        <v>10</v>
+      </c>
+      <c r="D23">
+        <v>40</v>
+      </c>
+      <c r="E23" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A25">
+        <v>3</v>
+      </c>
+      <c r="B25" t="s">
+        <v>34</v>
+      </c>
+      <c r="C25">
+        <v>12</v>
+      </c>
+      <c r="D25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A26">
+        <v>3</v>
+      </c>
+      <c r="B26" t="s">
+        <v>35</v>
+      </c>
+      <c r="C26">
+        <v>12</v>
+      </c>
+      <c r="D26">
+        <v>-30</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A27">
+        <v>3</v>
+      </c>
+      <c r="B27" t="s">
+        <v>36</v>
+      </c>
+      <c r="C27">
+        <v>12</v>
+      </c>
+      <c r="D27">
+        <v>25</v>
+      </c>
+      <c r="E27" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A28">
+        <v>3</v>
+      </c>
+      <c r="B28" t="s">
+        <v>38</v>
+      </c>
+      <c r="C28">
+        <v>10</v>
+      </c>
+      <c r="D28">
+        <v>10</v>
+      </c>
+      <c r="E28" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A29">
+        <v>3</v>
+      </c>
+      <c r="B29" t="s">
+        <v>39</v>
+      </c>
+      <c r="C29">
+        <v>16</v>
+      </c>
+      <c r="D29">
+        <v>200</v>
+      </c>
+      <c r="E29" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A30">
+        <v>3</v>
+      </c>
+      <c r="B30" t="s">
+        <v>41</v>
+      </c>
+      <c r="C30">
+        <v>18</v>
+      </c>
+      <c r="D30">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A31">
+        <v>3</v>
+      </c>
+      <c r="B31" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31">
+        <v>18</v>
+      </c>
+      <c r="D31">
+        <v>-50</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A32">
+        <v>3</v>
+      </c>
+      <c r="B32" t="s">
+        <v>43</v>
+      </c>
+      <c r="C32">
+        <v>18</v>
+      </c>
+      <c r="D32">
+        <v>25</v>
+      </c>
+      <c r="E32" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A33">
+        <v>3</v>
+      </c>
+      <c r="B33" t="s">
+        <v>45</v>
+      </c>
+      <c r="C33">
+        <v>9</v>
+      </c>
+      <c r="D33">
+        <v>10</v>
+      </c>
+      <c r="E33" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A34">
+        <v>3</v>
+      </c>
+      <c r="B34" t="s">
+        <v>47</v>
+      </c>
+      <c r="C34">
+        <v>30</v>
+      </c>
+      <c r="D34">
+        <v>350</v>
+      </c>
+      <c r="E34" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A35">
+        <v>3</v>
+      </c>
+      <c r="B35" t="s">
+        <v>49</v>
+      </c>
+      <c r="C35">
+        <v>20</v>
+      </c>
+      <c r="D35">
+        <v>110</v>
+      </c>
+      <c r="E35" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A36">
+        <v>3</v>
+      </c>
+      <c r="B36" t="s">
+        <v>51</v>
+      </c>
+      <c r="C36">
+        <v>20</v>
+      </c>
+      <c r="D36">
+        <v>-110</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A37">
+        <v>3</v>
+      </c>
+      <c r="B37" t="s">
+        <v>52</v>
+      </c>
+      <c r="C37">
+        <v>20</v>
+      </c>
+      <c r="D37">
+        <v>100</v>
+      </c>
+      <c r="E37" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A39">
+        <v>4</v>
+      </c>
+      <c r="B39" t="s">
+        <v>54</v>
+      </c>
+      <c r="C39">
+        <v>12</v>
+      </c>
+      <c r="D39">
+        <v>25</v>
+      </c>
+      <c r="E39" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A40">
+        <v>4</v>
+      </c>
+      <c r="B40" t="s">
+        <v>56</v>
+      </c>
+      <c r="C40">
+        <v>12</v>
+      </c>
+      <c r="D40">
+        <v>-25</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A41">
+        <v>4</v>
+      </c>
+      <c r="B41" t="s">
+        <v>57</v>
+      </c>
+      <c r="C41">
+        <v>12</v>
+      </c>
+      <c r="D41">
+        <v>25</v>
+      </c>
+      <c r="E41" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A42">
+        <v>4</v>
+      </c>
+      <c r="B42" t="s">
+        <v>60</v>
+      </c>
+      <c r="C42">
+        <v>20</v>
+      </c>
+      <c r="D42">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A43">
+        <v>4</v>
+      </c>
+      <c r="B43" t="s">
+        <v>61</v>
+      </c>
+      <c r="C43">
+        <v>20</v>
+      </c>
+      <c r="D43">
+        <v>-60</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A44">
+        <v>4</v>
+      </c>
+      <c r="B44" t="s">
+        <v>62</v>
+      </c>
+      <c r="C44">
+        <v>20</v>
+      </c>
+      <c r="D44">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A45">
+        <v>4</v>
+      </c>
+      <c r="B45" t="s">
+        <v>63</v>
+      </c>
+      <c r="C45">
+        <v>20</v>
+      </c>
+      <c r="D45">
+        <v>60</v>
+      </c>
+      <c r="E45" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A46">
+        <v>4</v>
+      </c>
+      <c r="B46" t="s">
+        <v>64</v>
+      </c>
+      <c r="C46">
+        <v>30</v>
+      </c>
+      <c r="D46">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A48">
+        <v>5</v>
+      </c>
+      <c r="B48" t="s">
+        <v>65</v>
+      </c>
+      <c r="C48">
+        <v>8</v>
+      </c>
+      <c r="D48">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A49">
+        <v>5</v>
+      </c>
+      <c r="B49" t="s">
+        <v>66</v>
+      </c>
+      <c r="C49">
+        <v>8</v>
+      </c>
+      <c r="D49">
+        <v>-25</v>
+      </c>
+      <c r="E49" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A50">
+        <v>5</v>
+      </c>
+      <c r="B50" t="s">
+        <v>67</v>
+      </c>
+      <c r="C50">
+        <v>8</v>
+      </c>
+      <c r="D50">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A51">
+        <v>5</v>
+      </c>
+      <c r="B51" t="s">
+        <v>68</v>
+      </c>
+      <c r="C51">
+        <v>8</v>
+      </c>
+      <c r="D51">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A52">
+        <v>5</v>
+      </c>
+      <c r="B52" t="s">
+        <v>69</v>
+      </c>
+      <c r="C52">
+        <v>8</v>
+      </c>
+      <c r="D52">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="A53">
+        <v>5</v>
+      </c>
+      <c r="B53" t="s">
+        <v>70</v>
+      </c>
+      <c r="C53">
+        <v>8</v>
+      </c>
+      <c r="D53">
+        <v>25</v>
+      </c>
+      <c r="E53" t="s">
+        <v>71</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
     <tabColor theme="8" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="C46:U65"/>
+  <dimension ref="A47:A65"/>
   <sheetFormatPr defaultColWidth="19.75" defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="46" spans="3:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="47" spans="3:16" s="1" customFormat="1" ht="97.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="C47" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="E47" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="F47" s="2"/>
-      <c r="G47" s="2"/>
-      <c r="K47" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="L47" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="M47" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="N47" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="O47" s="2"/>
-      <c r="P47" s="2"/>
-    </row>
-    <row r="48" spans="3:16" s="1" customFormat="1" ht="97.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="C48" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E48" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="F48" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K48" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L48" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="M48" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="N48" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="O48" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="P48" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="49" spans="3:21" s="1" customFormat="1" ht="97.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="C49" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E49" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="F49" s="2"/>
-      <c r="G49" s="2"/>
-      <c r="K49" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="L49" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="M49" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="N49" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="O49" s="2"/>
-      <c r="P49" s="2"/>
-    </row>
-    <row r="50" spans="3:21" s="1" customFormat="1" ht="97.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="C50" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E50" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="K50" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L50" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="M50" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="N50" s="2"/>
-      <c r="O50" s="2"/>
-      <c r="P50" s="2"/>
-    </row>
-    <row r="51" spans="3:21" s="1" customFormat="1" ht="97.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="52" spans="3:21" s="1" customFormat="1" ht="97.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="53" spans="3:21" s="1" customFormat="1" ht="97.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
-    <row r="54" spans="3:21" ht="106.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="C54" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="G54" s="3"/>
-      <c r="H54" s="3"/>
-      <c r="I54" s="3"/>
-      <c r="L54" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="M54" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="N54" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="O54" s="3"/>
-      <c r="P54" s="3"/>
-      <c r="Q54" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="R54" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="S54" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="T54" s="3"/>
-      <c r="U54" s="3"/>
-    </row>
-    <row r="55" spans="3:21" ht="106.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="C55" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="G55" s="3"/>
-      <c r="H55" s="3"/>
-      <c r="I55" s="3"/>
-      <c r="L55" s="3"/>
-      <c r="M55" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="N55" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="O55" s="3"/>
-      <c r="P55" s="3"/>
-      <c r="Q55" s="3"/>
-      <c r="R55" s="3"/>
-      <c r="S55" s="3"/>
-      <c r="T55" s="3"/>
-      <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" ht="106.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="C56" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G56" s="3"/>
-      <c r="H56" s="3"/>
-      <c r="I56" s="3"/>
-      <c r="L56" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="M56" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="N56" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="O56" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="P56" s="3"/>
-      <c r="Q56" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="R56" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="S56" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="T56" s="3"/>
-      <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" ht="106.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="C57" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="L57" s="3"/>
-      <c r="M57" s="3"/>
-      <c r="N57" s="3"/>
-      <c r="O57" s="3"/>
-      <c r="P57" s="3"/>
-      <c r="Q57" s="3"/>
-      <c r="R57" s="3"/>
-      <c r="S57" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="T57" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="U57" s="3"/>
-    </row>
-    <row r="58" spans="3:21" ht="106.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="59" spans="3:21" ht="106.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="60" spans="3:21" ht="106.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="61" spans="3:21" ht="106.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="62" spans="3:21" ht="106.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="63" spans="3:21" ht="106.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="64" spans="3:21" ht="106.5" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="65" ht="106.5" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="47" s="1" customFormat="1" ht="27.75" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="48" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="49" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="50" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="51" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="52" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="53" s="1" customFormat="1" ht="14.25" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="54" ht="14.25" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="55" ht="14.25" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="56" ht="14.25" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="57" ht="14.25" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="58" ht="14.25" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="59" ht="14.25" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="60" ht="14.25" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="61" ht="14.25" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="62" ht="14.25" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="63" ht="14.25" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="64" ht="14.25" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="65" ht="14.25" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/FarmLife_仕様書.xlsx
+++ b/FarmLife_仕様書.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="8"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="ゲームの動き" sheetId="1" r:id="rId1"/>
@@ -21,6 +21,7 @@
     <sheet name="作物" sheetId="5" r:id="rId7"/>
     <sheet name="作物の種類" sheetId="10" r:id="rId8"/>
     <sheet name="パーク" sheetId="6" r:id="rId9"/>
+    <sheet name="パーク配置図" sheetId="11" r:id="rId10"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -32,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="162">
   <si>
     <t>Stage</t>
     <phoneticPr fontId="1"/>
@@ -652,6 +653,814 @@
     </rPh>
     <rPh sb="2" eb="4">
       <t>ヘンカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Stage 1</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鍬耐久値+5</t>
+    <rPh sb="0" eb="1">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>タイキュウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>チ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鍬耐久値+10</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鍬耐久値+20</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物出現数+3</t>
+  </si>
+  <si>
+    <t>作物出現数+5</t>
+    <rPh sb="0" eb="2">
+      <t>サクモツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シュツゲン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>スウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物出現数+10</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出現時間増加1/s</t>
+    <rPh sb="0" eb="2">
+      <t>シュツゲン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出現時間増加2/s</t>
+    <rPh sb="0" eb="2">
+      <t>シュツゲン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃力増加+2</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃力増加+4</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <rPh sb="3" eb="5">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>爆発耐性</t>
+    <rPh sb="0" eb="2">
+      <t>バクハツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>タイセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>毒耐性</t>
+    <rPh sb="0" eb="1">
+      <t>ドク</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>タイセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物追加 ナス</t>
+    <rPh sb="0" eb="2">
+      <t>サクモツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物追加 ニンジン</t>
+    <rPh sb="0" eb="2">
+      <t>サクモツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物価値×2</t>
+    <rPh sb="0" eb="2">
+      <t>サクモツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物追加金ニンジン</t>
+    <rPh sb="0" eb="2">
+      <t>サクモツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>キン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Stage 2</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鍬耐久値+20</t>
+    <rPh sb="0" eb="1">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>タイキュウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>チ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鍬耐久値+25</t>
+    <rPh sb="0" eb="1">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="1" eb="3">
+      <t>タイキュウ</t>
+    </rPh>
+    <rPh sb="3" eb="4">
+      <t>チ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鍬耐久値+30</t>
+    <rPh sb="0" eb="1">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="1" eb="4">
+      <t>タイキュウチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物出現数+10</t>
+    <rPh sb="0" eb="2">
+      <t>サクモツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シュツゲン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>スウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物出現数+15</t>
+    <rPh sb="0" eb="2">
+      <t>サクモツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シュツゲン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>スウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出現時間増加+3/s</t>
+    <rPh sb="0" eb="2">
+      <t>シュツゲン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出現時間増加+5/s</t>
+    <rPh sb="0" eb="2">
+      <t>シュツゲン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出現時間増加+5/s</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃力増加+5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃力増加+6</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃力増加+6</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物追加 かぼちゃ</t>
+    <rPh sb="0" eb="2">
+      <t>サクモツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物追加 金の柿</t>
+    <rPh sb="0" eb="2">
+      <t>サクモツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>キン</t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t>カキ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物追加 キノコ</t>
+    <rPh sb="0" eb="2">
+      <t>サクモツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物追加 金のかぼちゃ</t>
+    <rPh sb="0" eb="2">
+      <t>サクモツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>キン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Stage 3</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鍬耐久値+6</t>
+    <rPh sb="0" eb="4">
+      <t>クワタイキュウチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鍬耐久値+12</t>
+    <rPh sb="0" eb="4">
+      <t>クワタイキュウチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鍬耐久値+14</t>
+    <rPh sb="0" eb="4">
+      <t>クワタイキュウチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鍬耐久値+20</t>
+    <rPh sb="0" eb="4">
+      <t>クワタイキュウチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物出現数+5</t>
+    <rPh sb="0" eb="2">
+      <t>サクモツ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>シュツゲンスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物出現数+10</t>
+    <rPh sb="0" eb="2">
+      <t>サクモツ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>シュツゲンスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物出現数+15</t>
+    <rPh sb="0" eb="2">
+      <t>サクモツ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>シュツゲンスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物出現数+20</t>
+    <rPh sb="0" eb="2">
+      <t>サクモツ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>シュツゲンスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出現時間増加+3/s</t>
+    <rPh sb="0" eb="4">
+      <t>シュツゲンジカン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出現時間増加+5/s</t>
+    <rPh sb="0" eb="4">
+      <t>シュツゲンジカン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出現時間増加+7/s</t>
+    <rPh sb="0" eb="4">
+      <t>シュツゲンジカン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出現時間増加+9/s</t>
+    <rPh sb="0" eb="4">
+      <t>シュツゲンジカン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃力増加+4</t>
+    <rPh sb="0" eb="5">
+      <t>コウゲキリョクゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃力増加+6</t>
+    <rPh sb="0" eb="5">
+      <t>コウゲキリョクゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃力増加+8</t>
+    <rPh sb="0" eb="5">
+      <t>コウゲキリョクゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>砂塵耐性</t>
+    <rPh sb="0" eb="2">
+      <t>サジン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>タイセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物追加 スイカ</t>
+    <rPh sb="0" eb="2">
+      <t>サクモツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物追加 きゅうり</t>
+    <rPh sb="0" eb="4">
+      <t>サクモツツイカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物追加 金のメロン</t>
+    <rPh sb="0" eb="4">
+      <t>サクモツツイカ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>キン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物追加 金のスイカ</t>
+    <rPh sb="0" eb="4">
+      <t>サクモツツイカ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>キン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物価値×3</t>
+    <rPh sb="0" eb="2">
+      <t>サクモツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>カチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Stage 4</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鍬の使用回数+20</t>
+    <rPh sb="0" eb="1">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カイスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鍬の使用回数+25</t>
+    <rPh sb="0" eb="1">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="2" eb="6">
+      <t>シヨウカイスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鍬の使用回数+25</t>
+    <rPh sb="0" eb="1">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シヨウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>カイスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物出現数+10</t>
+    <rPh sb="0" eb="5">
+      <t>サクモツシュツゲンスウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出現時間+5/s</t>
+    <rPh sb="0" eb="4">
+      <t>シュツゲンジカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出現時間+3/s</t>
+    <rPh sb="0" eb="4">
+      <t>シュツゲンジカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出現時間+10/s</t>
+    <rPh sb="0" eb="4">
+      <t>シュツゲンジカン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃力+2</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃力+4</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>攻撃力+6</t>
+    <rPh sb="0" eb="3">
+      <t>コウゲキリョク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>爆発耐性</t>
+    <rPh sb="0" eb="4">
+      <t>バクハツタイセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>毒耐性</t>
+    <rPh sb="0" eb="3">
+      <t>ドクタイセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>凍結耐性</t>
+    <rPh sb="0" eb="2">
+      <t>トウケツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>タイセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物追加 大根</t>
+    <rPh sb="0" eb="2">
+      <t>サクモツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ツイカ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ダイコン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物追加 金の大根</t>
+    <rPh sb="0" eb="4">
+      <t>サクモツツイカ</t>
+    </rPh>
+    <rPh sb="5" eb="6">
+      <t>キン</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>ダイコン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Stage 5</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鍬の耐久値+20</t>
+    <rPh sb="0" eb="1">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>タイキュウチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鍬の耐久値+25</t>
+    <rPh sb="0" eb="1">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="2" eb="5">
+      <t>タイキュウチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物出現数増加+5</t>
+    <rPh sb="0" eb="2">
+      <t>サクモツ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>シュツゲン</t>
+    </rPh>
+    <rPh sb="4" eb="5">
+      <t>スウ</t>
+    </rPh>
+    <rPh sb="5" eb="7">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物出現数増加+10</t>
+    <rPh sb="0" eb="7">
+      <t>サクモツシュツゲンスウゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物出現数増加+5</t>
+    <rPh sb="0" eb="7">
+      <t>サクモツシュツゲンスウゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出現数増加+5/s</t>
+    <rPh sb="0" eb="5">
+      <t>シュツゲンスウゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>週出現数増加+3/s</t>
+    <rPh sb="0" eb="1">
+      <t>シュウ</t>
+    </rPh>
+    <rPh sb="1" eb="6">
+      <t>シュツゲンスウゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出現時間増加5/s</t>
+    <rPh sb="0" eb="2">
+      <t>シュツゲン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出現時間増加+10/s</t>
+    <rPh sb="0" eb="6">
+      <t>シュツゲンジカンゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>麻痺耐性</t>
+    <rPh sb="0" eb="2">
+      <t>マヒ</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>タイセイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Stage 6</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鍬耐久値+6</t>
+    <rPh sb="0" eb="1">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="1" eb="4">
+      <t>タイキュウチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鍬耐久値+12</t>
+    <rPh sb="0" eb="1">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="1" eb="4">
+      <t>タイキュウチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鍬耐久値+14</t>
+    <rPh sb="0" eb="1">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="1" eb="4">
+      <t>タイキュウチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>鍬耐久値+20</t>
+    <rPh sb="0" eb="1">
+      <t>クワ</t>
+    </rPh>
+    <rPh sb="1" eb="4">
+      <t>タイキュウチ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>作物出現数増加+10</t>
+    <rPh sb="0" eb="2">
+      <t>サクモツ</t>
+    </rPh>
+    <rPh sb="2" eb="7">
+      <t>シュツゲンスウゾウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>出現時間増加+2/s</t>
+    <rPh sb="0" eb="2">
+      <t>シュツゲン</t>
+    </rPh>
+    <rPh sb="2" eb="4">
+      <t>ジカン</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ゾウカ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -693,12 +1502,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -707,11 +1531,14 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -12992,6 +13819,562 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K36"/>
+  <sheetFormatPr defaultColWidth="20.5" defaultRowHeight="119.25" customHeight="1" x14ac:dyDescent="0.4"/>
+  <sheetData>
+    <row r="1" spans="1:11" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="2" spans="1:11" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F2" s="2"/>
+      <c r="G2" s="2"/>
+      <c r="H2" s="2"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" spans="1:11" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="F4" s="2"/>
+      <c r="G4" s="2"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:11" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C5" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:11" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="J6" s="2"/>
+    </row>
+    <row r="7" spans="1:11" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="8" spans="1:11" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>90</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+    </row>
+    <row r="9" spans="1:11" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C9" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C10" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="F10" s="2"/>
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+    </row>
+    <row r="11" spans="1:11" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C11" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I11" s="2"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+    </row>
+    <row r="12" spans="1:11" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C12" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2"/>
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+    </row>
+    <row r="13" spans="1:11" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="14" spans="1:11" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>106</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+    </row>
+    <row r="15" spans="1:11" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C15" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C16" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+    </row>
+    <row r="17" spans="1:11" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C17" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="F17" s="2"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="I17" s="2"/>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+    </row>
+    <row r="18" spans="1:11" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C18" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+    </row>
+    <row r="19" spans="1:11" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="20" spans="1:11" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>128</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+    </row>
+    <row r="21" spans="1:11" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C21" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C22" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+    </row>
+    <row r="23" spans="1:11" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C23" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C24" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+    </row>
+    <row r="25" spans="1:11" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="26" spans="1:11" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>144</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+    </row>
+    <row r="27" spans="1:11" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C27" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+    </row>
+    <row r="28" spans="1:11" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C28" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+    </row>
+    <row r="29" spans="1:11" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C29" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C30" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+    </row>
+    <row r="31" spans="1:11" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="32" spans="1:11" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>155</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="33" spans="3:6" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C33" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="F33" s="2"/>
+    </row>
+    <row r="34" spans="3:6" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C34" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="F34" s="2"/>
+    </row>
+    <row r="35" spans="3:6" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C35" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="36" spans="3:6" ht="119.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C36" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
